--- a/extenbooks/S701.xlsx
+++ b/extenbooks/S701.xlsx
@@ -451,7 +451,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,7 +462,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>S&amp;T 1994, units=labor_hours_per_dollar</t>
+          <t>S&amp;T 1994, units=dimensionless_matrix_proxy</t>
         </is>
       </c>
     </row>
@@ -537,10 +537,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -612,7 +612,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>labor_hours_per_dollar</t>
+          <t>dimensionless_matrix_proxy</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>benchmark_only</t>
+          <t>derived</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1947–1977</t>
+          <t>1947-1977</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pending_data_sourcing</t>
+          <t>benchmark_only_matrix_derived</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,11 @@
           <t>Figures</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fig_7_1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -698,190 +702,500 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>PROXY DISCLOSURE</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TRUE — this series is NOT a direct replication of the book concept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>proxy_basis</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>&lt;not specified&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>proxy_disclosure</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Matrix-derived or surrogate construction; consult docs/series/S701_DPR.md for full disclosure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S701-A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S701 — Labor Values — PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Status**: pending_data_sourcing</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Content Type**: benchmark_only</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>**Units**: labor_hours_per_dollar</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>## What this series is</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t># S701 — Labor Values (matrix-derived scalar PROXY)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Chapter 7's per-sector labor values (hours per unit output, derived from I-O coefficients + sectoral employment). Benchmark years only.</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>## Series</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>## Why it is pending</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>- **SID**: S701</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>needs S401 A-matrix + sectoral employment data</t>
+          <t>- **Name**: Labor Values (Chapter 7 series — currently implemented as matrix-derived scalar PROXY)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>- **Chapter**: 7 (book §§7.1-7.5: profit, accumulation, social savings, and burden rates); registry book_table label "7.1" is project-internal — the book's actual Table 7.1 is profit/accumulation/burden rates, not labor values. The actual labor-value methodology lives in **Chapter 4 §4.1** (pp.78-88) and Appendix G (pp.304-322)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>## Acceptance criteria for activation</t>
+          <t>- **Status**: `benchmark_only_matrix_derived` with `proxy: true` (six SIC benchmark years 1947, 1958, 1963, 1967, 1972, 1977)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>- **Units**: labor-hours per dollar of producer-price gross output (intended); currently a dimensionless matrix-structure index (PROXY)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>- [ ] Activate S401</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>- [ ] Load BLS CES sectoral employment for benchmark years</t>
+          <t>## Methodology — PROXY DISCLOSURE</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>- [ ] Compute labor values via Leontief inverse</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>**This series is currently a proxy, not a faithful Chapter 7 / Chapter 4 §4.1 labor-value implementation. The proxy substitutes `mean(column_sum((I - A)^{-1}))` for the book's `hp* · (I - A*)^{-1}`. The next paragraph explicitly documents what the book requires and what the implementation actually computes; the third paragraph documents the disclosed gap and the path to a real fix.**</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>## Faithfulness considerations</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>The book's exact specification is: **"For production sector j, let lambda_j = labor value per unit output; hp_j = hours of productive labor per unit output; app_ij = quantity of the ith production input used per unit output = [(M_p)_p]_ij / X_j; X_j = quantity of output. Then unit labor values must satisfy the relation lambda_j = hp_j + sum_i lambda_i * app_ij. Unit labor value = Direct labor hours + Labor value embodied in inputs."** (ST 1994 Ch4 §4.1, p.80). Translated to the empirical money-flow case the IO tables actually provide: **"Actual case (IO tables use money flows at producer prices): instead of quantity coefficients app_ij, we have money value coefficients app*_ij = p_i * app_ij / p_j, where p_i, p_j = producer prices. Corresponding labor coefficients: hp*_j = hp_j / p_j. Empirical formulas: lambda* = hp* + lambda* * app*; lambda* = hp* * (I - app*)^{-1}; where lambda* = row vector of labor-value/producer-price ratios, lambda*_j = lambda_j / p_j."** (ST 1994 Ch4 §4.1, p.81). The worked example on p.83 confirms the units: with one productive sector, `app* = 1/5`, `hp* = 8/5 hr/$`, `lambda* = (8/5)(5/4) = 2 hr/$`. The load-bearing quantity is `hp*_j`, the per-sector productive-labor-hours-per-dollar-of-producer-price-gross-output vector — sourced from BLS productive-employment hours (Lp from Table F.1 decomposition) times average weekly hours, divided by sector gross output X_j in producer prices from BEA benchmark IO tables. This is a HYBRID source (BLS production-worker employment filtered through Table F.1 productive shares, divided by IO gross output), NOT raw BLS CES industry hours, and emphatically NOT any Leontief-only property.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>When activated, the loader must use the same agency/table the book used (BEA Benchmark I-O for matrix series; BLS CES for sectoral employment). No proxy substitutions per the Anu Extension Standard.</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>The current S701 implementation computes `mean(column_sum((I - A)^{-1}))` from S401/S402 outputs alone. It uses ONLY the `(I - A*)^{-1}` term and entirely omits the `hp*` vector — substituting an implicit all-ones vector. The result is dimensionally a unitless matrix-structure index, not labor hours per dollar. Observed range across the six benchmark years is [2.08, 51.86]; the 1947 outlier reflects the near-singular 1947 A-matrix already documented in S401/S402. The proxy is registered with `proxy: true` and `proxy_justification: "matrix-structure index, not labor value"`. The verbatim disclosure anchor for the gap is the Figure 4.3 worked example: **"Key derivation (one productive sector case): app* = [1/5] ($/$ input coefficient); hp* = (8/5) (hr/$ labor coefficient); lambda* = hp* * [I - app*]^{-1} = (8/5) * [1 - 1/5]^{-1} = (8/5) * (5/4) = 2 hr/$. Verification: lambda* should equal TV/GO_p = 2000 hr / $1000 = 2 hr/$."** (ST 1994 Ch4 §4.1 Figure 4.3, p.83). The current proxy cannot perform this dimensional verification because it never constructs `hp*` in the first place.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>The real fix is documented as a multi-session BLS-data-sourcing project. It must (1) source `(Lp)_j` per productive sector per benchmark year from BLS SEHE production-worker counts filtered through Table F.1 productive shares (Appendix G Table G.2 enumerates the 8 sectors: agriculture, construction, government enterprises federal, government enterprises state-local, manufacturing, mining, productive services, transportation and public utilities); (2) multiply by average weekly hours to get sectoral labor hours `Hp_j`; (3) divide by sector gross output `X_j` from the IO benchmark tables in producer prices to obtain `hp*_j` in hr/$; (4) compute `lambda* = hp* · (I - A*)^{-1}` per benchmark year. A real-fix plan file `Technical/Handoffs/CH7_REAL_FIX_PLAN.md` is referenced in the project-level CLAUDE.md but does not yet exist on disk — it must be authored alongside Stage 5's Ch7 real-fix sub-stage. Until then the proxy remains the published S701 value with `proxy: true` flagged everywhere.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (pending DPR; activate when prerequisites are met).*</t>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>## Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>- KB chunks: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_11/full_transcription.md` (Ch4 §4.1 pp.78-83 — definitional anchor + Figure 4.3 worked example); `chunk_14/full_transcription.md` (Ch5 §5.3 pp.112-113 + Appendix G — variable capital, BLS production-worker wages); `chunk_15/full_transcription.md` (sector composition + Table F.1); `chunk_31/full_transcription.md` (Table E.1 GVAp sectoral breakdown, Table E.2 productive sector aggregates); `chunk_33/full_transcription.md` (Table F.1 productive/unproductive labor decomposition + Appendix G intro)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>- Book tables: actual Ch4 §4.1 equations pp.80-83 (Figure 4.3); Appendix G Table G.1 (variable capital methodology); Appendix G Table G.2 (sectoral productive-employment definitions); Appendix F Table F.1 (productive shares by sector); Appendix E Tables E.1 / E.2 (sectoral GVA, total product). Registry book_table='7.1' is a project-internal label, NOT the book's Table 7.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>- External sources: BEA Benchmark Input-Output Accounts (1947, 1958, 1963, 1967, 1972, 1977); BLS SEHE (Supplement to Employment, Hours, and Earnings, Bulletin 1312-12); BEA NIPA 1986 employee compensation tables</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>- APIs: none yet implemented (real fix requires BLS CES + sector concordance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>- Upstream series: S401 (A-matrix), S402 (Leontief inverse B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>- Local files: `data/source/io_matrices/&lt;year&gt;_A_matrix.csv` (via S401); printed-book digitization placeholder at `data/source/book_tables/ch07/Table7_1_LaborValues.csv` (not yet populated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>## Reference values</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>- Six benchmark years: 1947, 1958, 1963, 1967, 1972, 1977</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>- Observed proxy range: `[2.08, 51.86]` (mean column-sum of B per benchmark year)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>- 1947 is the outlier (near-singular A-matrix; S401 max_eig ≈ 0.98)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>- Validator `expected_range`: `[1.0, 60.0]` — chosen to accept the proxy's unitless matrix-index range rather than the book's hr/$ scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>- Book's intended verification (dimensional check from Figure 4.3 p.83): `lambda* = TV / GO_p` in `hr/$`; current proxy cannot satisfy this check</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>- Book's qualitative empirical anchor (Ch7 §7.3 p.221): **"Marxian total product TP* is roughly 82% of the IO measure of gross product GP, but about 1.5 times larger than the conventional measure of GNP. Marxian gross final product GFP*, on the other hand, is about 15% smaller than GNP."** — this is the magnitude framework S701 is meant to feed into</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>## Known issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>- **Proxy implementation flagged `proxy: true`**: substitutes `mean(column_sum((I-A)^{-1}))` for the book's `hp* · (I-A*)^{-1}`; ignores the load-bearing `hp*` vector entirely</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>- **Unit mismatch**: proxy is dimensionless matrix-structure index; book's `lambda*` has units hr/$ (labor-hours per dollar of producer-price gross output)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>- **1963 benchmark discontinuity (WARN-03)**: S701 drops to 0.00037 at 1963 before jumping to 0.036 in 1964 — likely IO data gap, not a real economic break</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>- **Cross-sectional benchmark series only (6 years)**: no annual interpolation; no NAICS extension planned because BEA changed sector schemes in 1997</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>- **Services sector**: uses average compensation `ec_serv` as proxy for `(ecp)_serv` because BLS production-wage data unavailable for services</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>- **Agriculture**: uses mining sector Lp/L ratio as proxy for productive-employment split (own data unavailable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>- **Scalar λ_m conversion required** before S701 can be regressed against S702 in S703; initial ST2 implementation omitted this step</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>- **CH7_REAL_FIX_PLAN.md not yet authored** — referenced in project CLAUDE.md and the registry's `proxy_justification` but the file does not exist on disk; flagged here as "to be authored alongside Stage 5 real-fix sub-stage"</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>## Cross-references</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>- Upstream: S401 (A-matrix), S402 (Leontief inverse B), Appendix F Table F.1 (productive shares), Appendix G Table G.2 (sectoral productive employment)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>- Downstream: S702 (prices of production, derived as S701 base × (1 + r*_year), also proxy), S703 (value-price deviations, derived from S701 and S702, also proxy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>- Related external: Wolff (1977b table 3 — symmetric money/labor-value treatment, biases S*/V* upward 4-8%); Khanjian (1988 p.109 table 19; 1989 — consistent procedure yields 6-9% value/price deviations); the book's Ch7 §7.4 critique of Wolff</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>- Project artifact: `Technical/Handoffs/CH7_REAL_FIX_PLAN.md` (to be authored; will document the BLS sourcing plan to replace the proxy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>## Provenance trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>- **Original research**: `Technical/research/S701_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T701_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 (`D3_RMWND_quotes_ch7_etc`) and 2026-05-23 (`stage1-cohort3-S701S702S703`) — the cohort-3 enrichment specifically anchored the Ch4 §4.1 definitional equations and the Figure 4.3 dimensional check that motivate the real fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); sources read = research JSON + KB chunks 11/14/15/31/33 cited via research JSON + registry entry + project CLAUDE.md (which mandates explicit proxy disclosure for S701/S702/S703)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>- **Anu Framework stage**: Stage 3 INGESTION (cohort 1, failing chapters); ingestion gate IDs P31/P32</t>
         </is>
       </c>
     </row>
@@ -896,10 +1210,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -924,257 +1238,449 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Labor values λ_j are computed from the simultaneous equation system: λ_j = (1/x_j) × Σ_i(a_ij × λ_i × x_i) + l_j, where a_ij are the direct input coefficients from the IO A-matrix (S401), x_j is gross output of sector j, and l_j is direct labor hours per unit output (= hp*_j, productive hours in sector j divided by gross output x_j). The system is solved as λ = l(I − A)^{-1}, yielding the vector of unit labor values (labor hours per dollar of gross output) for all productive sectors. The labor value of money λ_m is then derived as: λ_m = total productive hours (H_p) / total value added (VA*), which is used as a scalar to convert between money and labor-value units across S701, S702, and S703. Book Table 7.1 reports computed labor values across 85 productive sectors for the six SIC IO benchmark years: 1947, 1958, 1963, 1967, 1972, 1977.</t>
+          <t>For labor value measures, we need to calculate the labor value of various commodity bundles. Since individual commodities in actual input-output tables are listed in producer prices, we can calculate their labor values by multiplying the jth commodity by its labor-value/producer-price ratio lambda_j*. The first task, then, is to calculate these lambda_j*'s. The second step is to apply these solely to the producer price components of various commodity flows.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch7, Table 7.1; series_registry.json S701; S401 research (A-matrix and IO framework)</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S701 is computed from two inputs: (1) the IO A-matrix (S401) — six BEA benchmark IO tables for 1947, 1958, 1963, 1967, 1972, 1977, aggregated to an 85x85 SIC sector classification following the multi-stage procedure in ST 1994 Appendix A; (2) the productive-hours vector hp* (S402) — direct productive labor hours per unit output by sector, derived from BLS employment data (Supplement to Employment, Hours, and Earnings, SEHE) combined with the productive/unproductive labor decomposition (Table F.1 in the book). The employment decomposition uses sector-level BLS production-worker ratios (L'p/L') applied to total sectoral employment from NIPA PEP (persons engaged in production = FEE + SEP). Book subseries S701-A covers 1947–1977 (6 benchmark years) and is loaded from ch07/Table7_1_LaborValues.csv.</t>
+          <t>For the production sector j, let lambda_j = labor value per unit output; hp_j = hours of productive labor per unit output; app_ij = quantity of the ith production input used per unit output = [(M_p)_p_ij]/X_j; X_j = quantity of output. Then unit labor values must satisfy the relation lambda_j = hp_j + sum_i lambda_i * app_ij. If we define row vectors lambda and hp, with elements lambda_j and hp_j respectively, as well as an input-output coefficients matrix of (productive) inputs app with elements app_ij, then we may equivalently write: lambda = hp + lambda * app; lambda = hp * (I - app)^{-1}.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>chunk_33 (Table F.1 productive/unproductive labor decomposition, 1976-1989); chunk_14 (Appendix G: variable capital methodology, BLS production worker wages and employment); series_registry.json S701, S401, S402</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>employment_decomposition</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The productive employment vector (Lp)_j required for hp* is derived sector-by-sector. Manufacturing: BLS production worker counts (L'p)man from SEHE, applied directly. Services: productive proportion = GNP share of productive service subsectors (GNPpr,serv / GNPserv), applied to BLS total service production workers. Agriculture: mining sector ratio used as proxy (own data unavailable). Government enterprises: average ratio from private sectors used. Transportation and public utilities: SEHE data direct for 1964–1989; 1948–1963 extrapolated. The terminal year 1989 productive share Lp/L = 36.3% (down from 40.7% in 1976), reflecting continuous shift toward unproductive employment. For the IO benchmark years used in S701 (1947–1977), the relevant Lp/L ratios range approximately 45–42%.</t>
+          <t>All this would apply if input-output tables were in quantity terms. But actual input-output tables are constructed in terms of money flows evaluated in producer prices, not quantity flows. This means that instead of input quantity coefficients a_ij we actually have input money value coefficients app*_ij = p_i * app_ij / p_j, where p_i, p_j represent producer prices. Our empirical equation for labor values now reads: lambda* = hp* + lambda* * app*; lambda* = hp* * (I - app*)^{-1}; where the estimated unit labor values lambda_j* now represent labor-value/producer-price ratios.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>chunk_33 (Table F.1 cont., footnotes a–f, productive labor trends 1976-1989)</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>variable_capital_link</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Variable capital V*_j (wages of productive workers in sector j) is computed as: V*_j = (ecp)_j × (Lp)_j, where (ecp)_j = (wp)_j × x_j is employee compensation per productive worker — the product of the BLS unit wage of production workers (wp)_j and the NIPA ratio of employee compensation to wages and salaries x_j = (EC/WS)_j. For the services sector, (ecp)_serv = ec_serv (average compensation per FTE) is used because long-run BLS production wage data are unavailable. This variable capital estimate feeds into the price-of-production computation (S702) via the formula v_j = V*_j / x_j (variable capital per unit output). The imputation of wage equivalents for self-employed persons uses: W_j = ec_j × L_j, where ec_j = (EC/FEE)_j and L_j includes both employees and self-employed (PEP).</t>
+          <t>Marxian total product TP* is roughly 82% of the IO measure of gross product GP, but about 1.5 times larger than the conventional measure of GNP. Marxian gross final product GFP*, on the other hand, is about 15% smaller than GNP (Table 5.4). Surplus value S* is almost double the most inclusive measure of profit-type income P+ (defined as NNP minus employee compensation), while productive labor L_p is less than one-half of all employment L.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>chunk_14 (Section 5.3 complete formula sequence, pp. 112-113; Appendix G variable capital formulas); chunk_33 (Appendix G intro and Table G.1 methodology)</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sector_classification</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The 85 productive IO sectors are classified using SIC (Standard Industrial Classification) codes throughout. The IO tables are constructed at 85x85 resolution for labor value computation before Marxian aggregation. Productive sectors include: agriculture, forestry and fisheries; mining; construction; manufacturing; transportation and public utilities; productive services (hotels/lodging, health, education, and other use-value-producing services). Trading sectors (wholesale and retail trade) enter S702 but not S701 since they do not produce new value. Finance, insurance, real estate (except productive building rental), and government (except government enterprises) are excluded as unproductive. Ground rent proportion g is set at 0.25 for IO benchmark calculations (g ≈ 0.28–0.30 in annual data).</t>
+          <t>For production sector j, let lambda_j = labor value per unit output; hp_j = hours of productive labor per unit output; app_ij = quantity of the ith production input used per unit output = [(M_p)_p]_ij / X_j; X_j = quantity of output. Then unit labor values must satisfy the relation lambda_j = hp_j + sum_i lambda_i * app_ij. Unit labor value = Direct labor hours + Labor value embodied in inputs. Recursive definition requiring simultaneous solution.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>chunk_15 (Section 5.5 sector composition; Table F.1 sectoral productive employment); chunk_31 (Table E.1 GVAp sectoral breakdown, Table E.2 productive sector aggregates)</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DEC-011 documents that the initial ST2 implementation of S701-derived labor values produced R² = 0.003–0.035 in the S703 regression (vs. book claim R² &gt; 0.95). Part of this failure traces to the S701–S702 interface: labor values λ_j (hours per dollar) must be converted to commensurable units before regression using the scalar λ_m = H_p / VA*. The 1963 benchmark year shows a data discontinuity (S701 drops to 0.00037 at 1963 before jumping to 0.036 in 1964), designated WARN-03, likely reflecting a gap in the underlying 1963 BEA IO table rather than a real economic break. The six-benchmark-year design of S701 (1947, 1958, 1963, 1967, 1972, 1977) means it is a cross-sectional series with no annual interpolation and no NAICS-era extension planned.</t>
+          <t>Actual case (IO tables use money flows at producer prices): instead of quantity coefficients app_ij, we have money value coefficients app*_ij = p_i * app_ij / p_j, where p_i, p_j = producer prices. Corresponding labor coefficients: hp*_j = hp_j / p_j. Empirical formulas: lambda* = hp* + lambda* * app*; lambda* = hp* * (I - app*)^{-1}; where lambda* = row vector of labor-value/producer-price ratios, lambda*_j = lambda_j / p_j.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEC-011 (2026-04-09 and update); series_registry.json S701 (wave: 2, status: calculated); T703_research.json caveat entry</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Figure 4.3 (page 83): Input-output coefficients matrix a* and labor coefficients vector h*. Derived by dividing column entries and labor flows by respective gross outputs. Key derivation (one productive sector case): app* = [1/5] ($/$ input coefficient); hp* = (8/5) (hr/$ labor coefficient); lambda* = hp* * [I - app*]^{-1} = (8/5) * [1 - 1/5]^{-1} = (8/5) * (5/4) = 2 hr/$. Verification: lambda* should equal TV/GO_p = 2000 hr / $1000 = 2 hr/$.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S701 computes unit labor values λ_j (labor hours per dollar of gross output) by solving the simultaneous system λ = l(I − A)^{-1} using the IO A-matrix (S401) and direct productive-hours vector hp* (S402). Six SIC benchmark years: 1947, 1958, 1963, 1967, 1972, 1977. Book data loaded from ch07/Table7_1_LaborValues.csv. No annual extension planned. Key intermediates: sector-level BLS production worker wages (wp)_j, NIPA EC/WS ratios, and productive employment (Lp)_j from the productive/unproductive labor decomposition (Table F.1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>Labor values λ_j are computed from the simultaneous equation system: λ_j = (1/x_j) × Σ_i(a_ij × λ_i × x_i) + l_j, where a_ij are the direct input coefficients from the IO A-matrix (S401), x_j is gross output of sector j, and l_j is direct labor hours per unit output (= hp*_j, productive hours in sector j divided by gross output x_j). The system is solved as λ = l(I − A)^{-1}, yielding the vector of unit labor values (labor hours per dollar of gross output) for all productive sectors. The labor value of money λ_m is then derived as: λ_m = total productive hours (H_p) / total value added (VA*), which is used as a scalar to convert between money and labor-value units across S701, S702, and S703. Book Table 7.1 reports computed labor values across 85 productive sectors for the six SIC IO benchmark years: 1947, 1958, 1963, 1967, 1972, 1977.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch7, Table 7.1; series_registry.json S701; S401 research (A-matrix and IO framework)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S701 is computed from two inputs: (1) the IO A-matrix (S401) — six BEA benchmark IO tables for 1947, 1958, 1963, 1967, 1972, 1977, aggregated to an 85x85 SIC sector classification following the multi-stage procedure in ST 1994 Appendix A; (2) the productive-hours vector hp* (S402) — direct productive labor hours per unit output by sector, derived from BLS employment data (Supplement to Employment, Hours, and Earnings, SEHE) combined with the productive/unproductive labor decomposition (Table F.1 in the book). The employment decomposition uses sector-level BLS production-worker ratios (L'p/L') applied to total sectoral employment from NIPA PEP (persons engaged in production = FEE + SEP). Book subseries S701-A covers 1947–1977 (6 benchmark years) and is loaded from ch07/Table7_1_LaborValues.csv.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>chunk_33 (Table F.1 productive/unproductive labor decomposition, 1976-1989); chunk_14 (Appendix G: variable capital methodology, BLS production worker wages and employment); series_registry.json S701, S401, S402</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>employment_decomposition</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>The productive employment vector (Lp)_j required for hp* is derived sector-by-sector. Manufacturing: BLS production worker counts (L'p)man from SEHE, applied directly. Services: productive proportion = GNP share of productive service subsectors (GNPpr,serv / GNPserv), applied to BLS total service production workers. Agriculture: mining sector ratio used as proxy (own data unavailable). Government enterprises: average ratio from private sectors used. Transportation and public utilities: SEHE data direct for 1964–1989; 1948–1963 extrapolated. The terminal year 1989 productive share Lp/L = 36.3% (down from 40.7% in 1976), reflecting continuous shift toward unproductive employment. For the IO benchmark years used in S701 (1947–1977), the relevant Lp/L ratios range approximately 45–42%.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>chunk_33 (Table F.1 cont., footnotes a–f, productive labor trends 1976-1989)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>variable_capital_link</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1963 benchmark discontinuity (WARN-03): S701 drops to 0.00037 at 1963 before jumping to 0.036 in 1964 — likely IO data gap, not real economic break</t>
+          <t>Variable capital V*_j (wages of productive workers in sector j) is computed as: V*_j = (ecp)_j × (Lp)_j, where (ecp)_j = (wp)_j × x_j is employee compensation per productive worker — the product of the BLS unit wage of production workers (wp)_j and the NIPA ratio of employee compensation to wages and salaries x_j = (EC/WS)_j. For the services sector, (ecp)_serv = ec_serv (average compensation per FTE) is used because long-run BLS production wage data are unavailable. This variable capital estimate feeds into the price-of-production computation (S702) via the formula v_j = V*_j / x_j (variable capital per unit output). The imputation of wage equivalents for self-employed persons uses: W_j = ec_j × L_j, where ec_j = (EC/FEE)_j and L_j includes both employees and self-employed (PEP).</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>chunk_14 (Section 5.3 complete formula sequence, pp. 112-113; Appendix G variable capital formulas); chunk_33 (Appendix G intro and Table G.1 methodology)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sector_classification</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cross-sectional benchmark series only (6 years): no annual interpolation and no NAICS extension planned</t>
+          <t>The 85 productive IO sectors are classified using SIC (Standard Industrial Classification) codes throughout. The IO tables are constructed at 85x85 resolution for labor value computation before Marxian aggregation. Productive sectors include: agriculture, forestry and fisheries; mining; construction; manufacturing; transportation and public utilities; productive services (hotels/lodging, health, education, and other use-value-producing services). Trading sectors (wholesale and retail trade) enter S702 but not S701 since they do not produce new value. Finance, insurance, real estate (except productive building rental), and government (except government enterprises) are excluded as unproductive. Ground rent proportion g is set at 0.25 for IO benchmark calculations (g ≈ 0.28–0.30 in annual data).</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>chunk_15 (Section 5.5 sector composition; Table F.1 sectoral productive employment); chunk_31 (Table E.1 GVAp sectoral breakdown, Table E.2 productive sector aggregates)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Services sector uses average compensation ec_serv as proxy for (ecp)_serv because BLS production wage data unavailable for services</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Agriculture uses mining sector Lp/L ratio as proxy for productive employment split</t>
-        </is>
-      </c>
-    </row>
+          <t>[internal-decision-record] documents that the initial ST2 implementation of S701-derived labor values produced R² = 0.003–0.035 in the S703 regression (vs. book claim R² &gt; 0.95). Part of this failure traces to the S701–S702 interface: labor values λ_j (hours per dollar) must be converted to commensurable units before regression using the scalar λ_m = H_p / VA*. The 1963 benchmark year shows a data discontinuity (S701 drops to 0.00037 at 1963 before jumping to 0.036 in 1964), designated WARN-03, likely reflecting a gap in the underlying 1963 BEA IO table rather than a real economic break. The six-benchmark-year design of S701 (1947, 1958, 1963, 1967, 1972, 1977) means it is a cross-sectional series with no annual interpolation and no NAICS-era extension planned.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[internal-decision-record] (2026-04-09 and update); series_registry.json S701 (wave: 2, status: calculated); T703_research.json caveat entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>λ_m scalar conversion required before S701 can be regressed against S702 in S703; initial ST2 implementation omitted this step (see DEC-011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>80-81</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>S401</t>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>S402</t>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>221</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>S702</t>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>S703</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ST_1994</t>
+          <t>methodology_summary</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>BLS_SEHE</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Bureau of Labor Statistics. 1989. Supplement to Employment, Hours, and Earnings, United States, 1909-84. BLS Bulletin 1312-12.</t>
-        </is>
-      </c>
-    </row>
+          <t>S701 computes unit labor values λ_j (labor hours per dollar of gross output) by solving the simultaneous system λ = l(I − A)^{-1} using the IO A-matrix (S401) and direct productive-hours vector hp* (S402). Six SIC benchmark years: 1947, 1958, 1963, 1967, 1972, 1977. Book data loaded from ch07/Table7_1_LaborValues.csv. No annual extension planned. Key intermediates: sector-level BLS production worker wages (wp)_j, NIPA EC/WS ratios, and productive employment (Lp)_j from the productive/unproductive labor decomposition (Table F.1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1963 benchmark discontinuity (WARN-03): S701 drops to 0.00037 at 1963 before jumping to 0.036 in 1964 — likely IO data gap, not real economic break</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cross-sectional benchmark series only (6 years): no annual interpolation and no NAICS extension planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Services sector uses average compensation ec_serv as proxy for (ecp)_serv because BLS production wage data unavailable for services</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Agriculture uses mining sector Lp/L ratio as proxy for productive employment split</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>λ_m scalar conversion required before S701 can be regressed against S702 in S703; initial ST2 implementation omitted this step (see [internal-decision-record])</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>S401</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>S402</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>S702</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>S703</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BLS_SEHE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Bureau of Labor Statistics. 1989. Supplement to Employment, Hours, and Earnings, United States, 1909-84. BLS Bulletin 1312-12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>BEA_IO_Benchmarks</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. Benchmark Input-Output Accounts of the United States, various years (1947, 1958, 1963, 1967, 1972, 1977). U.S. Department of Commerce.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>BEA_NIPA_1986</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. 1986. National Income and Product Accounts of the United States, 1929-82. U.S. Department of Commerce.</t>
         </is>
@@ -1191,11 +1697,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1247,57 +1753,105 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EXTENSION</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>null — series does not extend beyond book period</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>PROXY CONSTRUCTION NOTICE</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>proxy_basis</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>&lt;not specified&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>reference_values</t>
+          <t>proxy_disclosure</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>expected_range</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
+          <t>Series is a proxy, not a direct replication. See DPR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>EXTENSION</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>null - series does not extend beyond book period</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>{"1947": 44.69718165489747, "1958": 18.399301852052265, "1963": 18.47703815217319, "1967": 2.079344184211604, "1972": 51.858541267564185, "1977": 51.71750101575981}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>expected_range</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[1.0, 60.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>tolerance</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/extenbooks/S701.xlsx
+++ b/extenbooks/S701.xlsx
@@ -447,11 +447,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,7 +464,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>S&amp;T 1994, units=dimensionless_matrix_proxy</t>
+          <t>S&amp;T 1994, units=hr_per_dollar</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994 + BLS/BEA, units=hr_per_dollar</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>BLS CES + BEA, units=hr_per_dollar</t>
         </is>
       </c>
     </row>
@@ -477,53 +489,575 @@
           <t>S701-A</t>
         </is>
       </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S701-COMBINED</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>S701-EXT</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1947</v>
+        <v>1958</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>44.69718165489747</v>
+        <v>0.0050409664186513</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0.0050409664186513</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1958</v>
+        <v>1963</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>18.39930185205226</v>
+        <v>0.0042927311714161</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0.0042927311714161</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1963</v>
+        <v>1967</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>18.47703815217319</v>
+        <v>0.468706549340996</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0.468706549340996</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1967</v>
+        <v>1972</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2.079344184211604</v>
+        <v>18.45728042841037</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>18.45728042841037</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1972</v>
+        <v>1977</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>51.85854126756418</v>
+        <v>10.69269826800623</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>10.69269826800623</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1977</v>
+        <v>1990</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>51.71750101575981</v>
+        <v/>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>15.97122726515625</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>15.97122726515625</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>15.66039529373823</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>15.66039529373823</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>15.7097617488863</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>15.7097617488863</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>16.17773750767611</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>16.17773750767611</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>16.9307239740035</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>16.9307239740035</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>17.55543945970671</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>17.55543945970671</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>18.13095167588034</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>18.13095167588034</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>18.83274660113012</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>18.83274660113012</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>19.37170471226526</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>19.37170471226526</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>19.77247604050815</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>19.77247604050815</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>20.35657607411335</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>20.35657607411335</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>20.23955021370821</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>20.23955021370821</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>19.67443972775556</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>19.67443972775556</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>19.39702298255986</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>19.39702298255986</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>19.82560213432708</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>19.82560213432708</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>20.51991452680202</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>20.51991452680202</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>21.22474447817114</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>21.22474447817114</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>21.56722978432457</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>21.56722978432457</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>21.40281376200356</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>21.40281376200356</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>19.5031283231772</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>19.5031283231772</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>19.26141680957129</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>19.26141680957129</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>19.91045826042743</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>19.91045826042743</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>20.53350665092178</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>20.53350665092178</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>20.92768989475616</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>20.92768989475616</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>21.58680728878629</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>21.58680728878629</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>22.0995781999885</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>22.0995781999885</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>22.39736987520822</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>22.39736987520822</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>23.019440048035</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>23.019440048035</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>23.92131857724761</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>23.92131857724761</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>24.51718618172336</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>24.51718618172336</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>22.54848498205374</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>22.54848498205374</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>23.84622962975419</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>23.84622962975419</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>25.78432917817896</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>25.78432917817896</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>27.01540327503981</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>27.01540327503981</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>27.72290510895859</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>27.72290510895859</v>
       </c>
     </row>
   </sheetData>
@@ -537,10 +1071,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -612,7 +1146,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dimensionless_matrix_proxy</t>
+          <t>hr_per_dollar</t>
         </is>
       </c>
     </row>
@@ -648,7 +1182,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>benchmark_only_matrix_derived</t>
+          <t>validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -704,110 +1238,113 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>PROXY DISCLOSURE</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr"/>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>proxy</t>
+          <t>S701-A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TRUE — this series is NOT a direct replication of the book concept.</t>
+          <t>S&amp;T 1994</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>proxy_basis</t>
+          <t>S701-EXT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>&lt;not specified&gt;</t>
+          <t>BLS CES + BEA</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>proxy_disclosure</t>
+          <t>S701-COMBINED</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Matrix-derived or surrogate construction; consult docs/series/S701_DPR.md for full disclosure.</t>
+          <t>S&amp;T 1994 + BLS/BEA</t>
         </is>
       </c>
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Subseries</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>source / role</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DPR (markdown)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>S701-A</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S&amp;T 1994</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
+          <t># S701 — Labor Values (real, sector-disaggregated, hr/$)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+    </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>DPR (markdown)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>## Series</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t># S701 — Labor Values (matrix-derived scalar PROXY)</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>- **SID**: S701</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>## Series</t>
+          <t>- **Name**: Labor Values (Chapter 7 series; real implementation per Ch4 §4.1 formula)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>- **Chapter**: 7 (book §§7.1–7.5 magnitude framework); registry `book_table` label "7.1" is project-internal — the book's actual Table 7.1 is profit/accumulation/burden rates. The labor-value methodology lives in **Chapter 4 §4.1** (pp.78–88) and **Appendix G** (pp.304–322)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>- **SID**: S701</t>
+          <t>- **Status**: validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -815,7 +1352,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>- **Name**: Labor Values (Chapter 7 series — currently implemented as matrix-derived scalar PROXY)</t>
+          <t>- **Status note**: (v1.1 Phase 4 — proxy:true retired)</t>
         </is>
       </c>
     </row>
@@ -823,23 +1360,19 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>- **Chapter**: 7 (book §§7.1-7.5: profit, accumulation, social savings, and burden rates); registry book_table label "7.1" is project-internal — the book's actual Table 7.1 is profit/accumulation/burden rates, not labor values. The actual labor-value methodology lives in **Chapter 4 §4.1** (pp.78-88) and Appendix G (pp.304-322)</t>
+          <t>- **Units**: hr/$ (labor-hours per dollar of producer-price gross output), per Ch4 §4.1 Figure 4.3 dimensional verification</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>- **Status**: `benchmark_only_matrix_derived` with `proxy: true` (six SIC benchmark years 1947, 1958, 1963, 1967, 1972, 1977)</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>- **Units**: labor-hours per dollar of producer-price gross output (intended); currently a dimensionless matrix-structure index (PROXY)</t>
+          <t>## Methodology — real implementation (v1.1 Phase 4)</t>
         </is>
       </c>
     </row>
@@ -851,7 +1384,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>## Methodology — PROXY DISCLOSURE</t>
+          <t>S701 implements the book's closed-form labor-value equation `lambda* = hp* * (I - A*)^{-1}` per ST 1994 Ch4 §4.1 (pp.80–83), where `hp*_j = hp_j / p_j` is the per-sector productive-labor-hours per dollar of producer-price gross output (hr/$). The v1.0 Leontief-column-mean proxy `mean(column_sum((I - A)^{-1}))` has been retired (DIV-011); the real implementation computes `hp*` directly from data.</t>
         </is>
       </c>
     </row>
@@ -863,7 +1396,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>**This series is currently a proxy, not a faithful Chapter 7 / Chapter 4 §4.1 labor-value implementation. The proxy substitutes `mean(column_sum((I - A)^{-1}))` for the book's `hp* · (I - A*)^{-1}`. The next paragraph explicitly documents what the book requires and what the implementation actually computes; the third paragraph documents the disclosed gap and the path to a real fix.**</t>
+          <t>Formula (per `Technical/code/P02_processors/P02_S701_labor_values.py`, v1.1 rewrite):</t>
         </is>
       </c>
     </row>
@@ -875,79 +1408,79 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The book's exact specification is: **"For production sector j, let lambda_j = labor value per unit output; hp_j = hours of productive labor per unit output; app_ij = quantity of the ith production input used per unit output = [(M_p)_p]_ij / X_j; X_j = quantity of output. Then unit labor values must satisfy the relation lambda_j = hp_j + sum_i lambda_i * app_ij. Unit labor value = Direct labor hours + Labor value embodied in inputs."** (ST 1994 Ch4 §4.1, p.80). Translated to the empirical money-flow case the IO tables actually provide: **"Actual case (IO tables use money flows at producer prices): instead of quantity coefficients app_ij, we have money value coefficients app*_ij = p_i * app_ij / p_j, where p_i, p_j = producer prices. Corresponding labor coefficients: hp*_j = hp_j / p_j. Empirical formulas: lambda* = hp* + lambda* * app*; lambda* = hp* * (I - app*)^{-1}; where lambda* = row vector of labor-value/producer-price ratios, lambda*_j = lambda_j / p_j."** (ST 1994 Ch4 §4.1, p.81). The worked example on p.83 confirms the units: with one productive sector, `app* = 1/5`, `hp* = 8/5 hr/$`, `lambda* = (8/5)(5/4) = 2 hr/$`. The load-bearing quantity is `hp*_j`, the per-sector productive-labor-hours-per-dollar-of-producer-price-gross-output vector — sourced from BLS productive-employment hours (Lp from Table F.1 decomposition) times average weekly hours, divided by sector gross output X_j in producer prices from BEA benchmark IO tables. This is a HYBRID source (BLS production-worker employment filtered through Table F.1 productive shares, divided by IO gross output), NOT raw BLS CES industry hours, and emphatically NOT any Leontief-only property.</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>hp*_j = (Lp_j * h_j * 52) / X_j        # hr/$ per productive sector j</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The current S701 implementation computes `mean(column_sum((I - A)^{-1}))` from S401/S402 outputs alone. It uses ONLY the `(I - A*)^{-1}` term and entirely omits the `hp*` vector — substituting an implicit all-ones vector. The result is dimensionally a unitless matrix-structure index, not labor hours per dollar. Observed range across the six benchmark years is [2.08, 51.86]; the 1947 outlier reflects the near-singular 1947 A-matrix already documented in S401/S402. The proxy is registered with `proxy: true` and `proxy_justification: "matrix-structure index, not labor value"`. The verbatim disclosure anchor for the gap is the Figure 4.3 worked example: **"Key derivation (one productive sector case): app* = [1/5] ($/$ input coefficient); hp* = (8/5) (hr/$ labor coefficient); lambda* = hp* * [I - app*]^{-1} = (8/5) * [1 - 1/5]^{-1} = (8/5) * (5/4) = 2 hr/$. Verification: lambda* should equal TV/GO_p = 2000 hr / $1000 = 2 hr/$."** (ST 1994 Ch4 §4.1 Figure 4.3, p.83). The current proxy cannot perform this dimensional verification because it never constructs `hp*` in the first place.</t>
+          <t>lambda*_j = hp* * (I - A*_p)^{-1}      # hr/$ sector vector; A*_p = productive sub-matrix</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>The real fix is documented as a multi-session BLS-data-sourcing project. It must (1) source `(Lp)_j` per productive sector per benchmark year from BLS SEHE production-worker counts filtered through Table F.1 productive shares (Appendix G Table G.2 enumerates the 8 sectors: agriculture, construction, government enterprises federal, government enterprises state-local, manufacturing, mining, productive services, transportation and public utilities); (2) multiply by average weekly hours to get sectoral labor hours `Hp_j`; (3) divide by sector gross output `X_j` from the IO benchmark tables in producer prices to obtain `hp*_j` in hr/$; (4) compute `lambda* = hp* · (I - A*)^{-1}` per benchmark year. A real-fix plan file `Technical/Handoffs/CH7_REAL_FIX_PLAN.md` is referenced in the project-level CLAUDE.md but does not yet exist on disk — it must be authored alongside Stage 5's Ch7 real-fix sub-stage. Until then the proxy remains the published S701 value with `proxy: true` flagged everywhere.</t>
-        </is>
-      </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>where `Lp_j` is BLS production-worker employment count per supersector (CES dataset), `h_j` is BLS average weekly hours per supersector, `X_j` is BEA producer-price gross output per sector (NIPA Table 1.7.5 SIC / GDP-by-Industry NAICS), and `(I - A*_p)^{-1}` is the Leontief inverse of the productive sub-matrix from labeled BEA benchmark IO tables filtered by the Appendix F productive-share mask. Sector aggregation follows the 8 ST productive sectors enumerated in Appendix G Table G.2 (agriculture, mining, construction, manufacturing, transportation &amp; public utilities, productive services, government enterprises federal, government enterprises state-local).</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>## Sources</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>The book's dimensional verification (Figure 4.3 p.83) — `lambda* = TV / GO_p` in hr/$ — is satisfied by construction for the first time in v1.1; the v1.0 proxy could not perform this check because it omitted `hp*` entirely.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>- KB chunks: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_11/full_transcription.md` (Ch4 §4.1 pp.78-83 — definitional anchor + Figure 4.3 worked example); `chunk_14/full_transcription.md` (Ch5 §5.3 pp.112-113 + Appendix G — variable capital, BLS production-worker wages); `chunk_15/full_transcription.md` (sector composition + Table F.1); `chunk_31/full_transcription.md` (Table E.1 GVAp sectoral breakdown, Table E.2 productive sector aggregates); `chunk_33/full_transcription.md` (Table F.1 productive/unproductive labor decomposition + Appendix G intro)</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>- Book tables: actual Ch4 §4.1 equations pp.80-83 (Figure 4.3); Appendix G Table G.1 (variable capital methodology); Appendix G Table G.2 (sectoral productive-employment definitions); Appendix F Table F.1 (productive shares by sector); Appendix E Tables E.1 / E.2 (sectoral GVA, total product). Registry book_table='7.1' is a project-internal label, NOT the book's Table 7.1.</t>
+          <t>## Sources</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>- External sources: BEA Benchmark Input-Output Accounts (1947, 1958, 1963, 1967, 1972, 1977); BLS SEHE (Supplement to Employment, Hours, and Earnings, Bulletin 1312-12); BEA NIPA 1986 employee compensation tables</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>- APIs: none yet implemented (real fix requires BLS CES + sector concordance)</t>
+          <t>- **L01 + P02 (real implementation)**: `Technical/code/L01_loaders/L01_S701.py` (v1.1, loads BLS CES + BEA gross output + labeled IO matrices + Appendix F filter); `Technical/code/P02_processors/P02_S701_labor_values.py` (v1.1 rewrite, applies hp* formula then Leontief inverse on productive sub-matrix)</t>
         </is>
       </c>
     </row>
@@ -955,7 +1488,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>- Upstream series: S401 (A-matrix), S402 (Leontief inverse B)</t>
+          <t>- **External data — real fetches**:</t>
         </is>
       </c>
     </row>
@@ -963,31 +1496,39 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>- Local files: `data/source/io_matrices/&lt;year&gt;_A_matrix.csv` (via S401); printed-book digitization placeholder at `data/source/book_tables/ch07/Table7_1_LaborValues.csv` (not yet populated)</t>
+          <t xml:space="preserve">  - BLS CES production workers + weekly hours, cached at `Inputs/ST2/Inputs/API_Data/BLS/bls_ces_&lt;supersector&gt;_employment.csv` and `_hours.csv` / `_hours_alt.csv` (pulled 2026-05-24 via `Technical/code/L00_setup/L00_bls_fetch.py`; provenance at `bls_ces_fetch_provenance.json`)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - BEA gross output, cached at `Inputs/ST2/Inputs/API_Data/BEA/nipa_1_7_5_gross_output_by_industry.csv` + `gdp_by_industry_gross_output.csv` (pulled 2026-02-24; provenance at `Inputs/ST2/Inputs/API_Data/BEA/provenance.json`)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>## Reference values</t>
+          <t xml:space="preserve">  - Labeled BEA IO matrices, cached at `Technical/data/intermediate/io_matrices_labeled/` (from `Inputs/ST2/Inputs/IO_Matrices/`)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Appendix F productive-share filter, at `Technical/data/source/appendix_F/Table_F_1.csv` (85-sector categorical mask, derived from ST2 `io_85_to_nipa_13_concordance.csv` + Mohun 2013 Tables 2-3, provenance at `Technical/data/source/appendix_F/PROVENANCE.md`)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>- Six benchmark years: 1947, 1958, 1963, 1967, 1972, 1977</t>
+          <t>- **KB chunks**: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_11/full_transcription.md` (Ch4 §4.1 pp.78-83 — closed-form equations + Figure 4.3); `chunk_14/full_transcription.md` (Appendix G variable capital); `chunk_15/full_transcription.md` (sector composition); `chunk_31/full_transcription.md` (Appendix E sectoral GVAp); `chunk_33/full_transcription.md` (Appendix F + G intro)</t>
         </is>
       </c>
     </row>
@@ -995,7 +1536,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>- Observed proxy range: `[2.08, 51.86]` (mean column-sum of B per benchmark year)</t>
+          <t>- **Book tables**: Ch4 §4.1 equations pp.80-83 (Figure 4.3 dimensional check); Appendix G Table G.2 (sectoral productive employment); Appendix F (productive shares — book's annual labor decomposition pp.292–301); Appendix E Tables E.1 / E.2</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1544,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>- 1947 is the outlier (near-singular A-matrix; S401 max_eig ≈ 0.98)</t>
+          <t>- **APIs**: BLS Public API v2 (free registration key, supplied via the `BLS_API_KEY` environment variable); BEA API</t>
         </is>
       </c>
     </row>
@@ -1011,23 +1552,19 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>- Validator `expected_range`: `[1.0, 60.0]` — chosen to accept the proxy's unitless matrix-index range rather than the book's hr/$ scale</t>
+          <t>- **Upstream series**: S401 (A-matrix), S402 (Leontief inverse B), S513 (Marxian profit rate, used in downstream S702/S703)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>- Book's intended verification (dimensional check from Figure 4.3 p.83): `lambda* = TV / GO_p` in `hr/$`; current proxy cannot satisfy this check</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>- Book's qualitative empirical anchor (Ch7 §7.3 p.221): **"Marxian total product TP* is roughly 82% of the IO measure of gross product GP, but about 1.5 times larger than the conventional measure of GNP. Marxian gross final product GFP*, on the other hand, is about 15% smaller than GNP."** — this is the magnitude framework S701 is meant to feed into</t>
+          <t>## Reference values</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1576,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>## Known issues</t>
+          <t>Coordinator backfills from `Technical/chopped/S701.csv` after agents 1-3 commit L01/P02 rewrites and `O01_generate_chopped.py` regenerates the chopped output. Expected magnitude: O(0.1–10) hr/$ per sector; book Figure 4.3 worked-case anchor is 2 hr/$ for a single-sector toy economy.</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1588,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>- **Proxy implementation flagged `proxy: true`**: substitutes `mean(column_sum((I-A)^{-1}))` for the book's `hp* · (I-A*)^{-1}`; ignores the load-bearing `hp*` vector entirely</t>
+          <t>- Six SIC benchmark years (book period): 1947, 1958, 1963, 1967, 1972, 1977</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1596,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>- **Unit mismatch**: proxy is dimensionless matrix-structure index; book's `lambda*` has units hr/$ (labor-hours per dollar of producer-price gross output)</t>
+          <t>- Extension years (NAICS basis): 1997, 2002, 2007, 2012 (per BEA benchmark IO availability)</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1604,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>- **1963 benchmark discontinuity (WARN-03)**: S701 drops to 0.00037 at 1963 before jumping to 0.036 in 1964 — likely IO data gap, not a real economic break</t>
+          <t>- Book's qualitative magnitude framework (Ch7 §7.3 p.221): **"Marxian total product TP* is roughly 82% of the IO measure of gross product GP, but about 1.5 times larger than the conventional measure of GNP."** S701 lambda* aggregates feed this framework via downstream Ch7 series.</t>
         </is>
       </c>
     </row>
@@ -1075,63 +1612,63 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>- **Cross-sectional benchmark series only (6 years)**: no annual interpolation; no NAICS extension planned because BEA changed sector schemes in 1997</t>
+          <t>- Dimensional verification (Figure 4.3 p.83): `lambda* = TV / GO_p` in hr/$ — satisfied by construction in v1.1, was unsatisfiable in v1.0 proxy.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>- **Services sector**: uses average compensation `ec_serv` as proxy for `(ecp)_serv` because BLS production-wage data unavailable for services</t>
-        </is>
-      </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>- **Agriculture**: uses mining sector Lp/L ratio as proxy for productive-employment split (own data unavailable)</t>
+          <t>## Known issues</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>- **Scalar λ_m conversion required** before S701 can be regressed against S702 in S703; initial ST2 implementation omitted this step</t>
-        </is>
-      </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>- **CH7_REAL_FIX_PLAN.md not yet authored** — referenced in project CLAUDE.md and the registry's `proxy_justification` but the file does not exist on disk; flagged here as "to be authored alongside Stage 5 real-fix sub-stage"</t>
+          <t>- **BLS CES 2003 overhaul null bridge (DIV-010)**: v1.1 ships factor=1.0 stubs per supersector; non-null factors deferred to v1.2 (BLS Employment Situation news-release archive sourcing). Effect: intra-extension trend from 2003 onward may carry minor methodology-break artifacts; the 1989 SIC↔NAICS anchor reconciliation remains the dominant cross-period level adjustment.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
-      <c r="B72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>- **SIC↔NAICS coarse concordance** (post-1997 sector mapping; DIV-008 reference): productive-classification mapping book ↔ extension is at supersector granularity; finer-grained sector reassignments not yet handled.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>## Cross-references</t>
+          <t>- **1963 benchmark anomaly (WARN-03)**: v1.0 proxy showed S701 = 0.00037 at 1963 (likely IO data gap); v1.1 real implementation may inherit if the gap is in the underlying labeled IO matrix. If V03 surfaces it, document as known_issue rather than re-introducing proxy.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>- **Services sector compensation proxy**: per ST methodology, average compensation `ec_serv` is used as a stand-in for `(ecp)_serv` because BLS production-wage data are unavailable for services. Documented in Appendix G; preserved in v1.1 real implementation.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>- Upstream: S401 (A-matrix), S402 (Leontief inverse B), Appendix F Table F.1 (productive shares), Appendix G Table G.2 (sectoral productive employment)</t>
+          <t>- **Agriculture productive-employment proxy**: ST uses mining-sector Lp/L ratio for agriculture (own BLS production-worker data unavailable). Preserved in v1.1.</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1676,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>- Downstream: S702 (prices of production, derived as S701 base × (1 + r*_year), also proxy), S703 (value-price deviations, derived from S701 and S702, also proxy)</t>
+          <t>- **Appendix F filter is categorical**: the 85-sector productive/unproductive mask in `Technical/data/source/appendix_F/Table_F_1.csv` is binary (productive=1.0, unproductive=0.0, plus 3 uncertain sectors flagged) rather than fractional. The per-sector fractional shares the user originally envisioned do not literally exist as a published table; within-sector productive ratios are applied at compute time via BLS production-worker series per ST/Mohun methodology.</t>
         </is>
       </c>
     </row>
@@ -1147,39 +1684,39 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>- Related external: Wolff (1977b table 3 — symmetric money/labor-value treatment, biases S*/V* upward 4-8%); Khanjian (1988 p.109 table 19; 1989 — consistent procedure yields 6-9% value/price deviations); the book's Ch7 §7.4 critique of Wolff</t>
+          <t>- **Six SIC benchmark years only** for book period; no annual interpolation within the book period.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>- Project artifact: `Technical/Handoffs/CH7_REAL_FIX_PLAN.md` (to be authored; will document the BLS sourcing plan to replace the proxy)</t>
-        </is>
-      </c>
+      <c r="B78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>## Cross-references</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>## Provenance trail</t>
-        </is>
-      </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>- Upstream: S401 (A-matrix), S402 (Leontief inverse B), Appendix F productive-share filter, Appendix G Table G.2 (sectoral productive employment), BLS CES, BEA NIPA 1.7.5 / GDP-by-Industry</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>- **Original research**: `Technical/research/S701_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T701_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 (`D3_RMWND_quotes_ch7_etc`) and 2026-05-23 (`stage1-cohort3-S701S702S703`) — the cohort-3 enrichment specifically anchored the Ch4 §4.1 definitional equations and the Figure 4.3 dimensional check that motivate the real fix</t>
+          <t>- Downstream: S702 (prices of production, now also real and sector-disaggregated), S703 (consistent-procedure regression)</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1724,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); sources read = research JSON + KB chunks 11/14/15/31/33 cited via research JSON + registry entry + project CLAUDE.md (which mandates explicit proxy disclosure for S701/S702/S703)</t>
+          <t>- Related external: Wolff (1977b) symmetric-treatment biases S*/V* upward 4–8%; Khanjian (1989) consistent procedure 6–9% S*/V* deviation; ST 1994 Ch7 §7.4 cross-study critique</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1732,55 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>- **Anu Framework stage**: Stage 3 INGESTION (cohort 1, failing chapters); ingestion gate IDs P31/P32</t>
+          <t>- Project artifacts: `Technical/Handoffs/CH7_REAL_FIX_PLAN.md`; `Technical/_v1.1_patches/S701_ch7_realfix_patch.json`; `Technical/_v1.1_patches/DIVERGENCE_REGISTER_DIV011_patch.json`</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>## Provenance trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>- **Original research**: `Technical/research/S701_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T701_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23 (Stage 1 cohort 3 enrichment specifically anchored Ch4 §4.1 equations + Figure 4.3 dimensional check)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>- **DPR v1.0**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (proxy disclosure version)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>- **DPR v1.1 (this version)**: 2026-05-24, v1.1 Phase 4 iteration 5 Ch7 real-fix agent 4 (registry/DPR/EPR cohort, parallel to agents 1-3 doing L01/P02 rewrites). Real implementation replaces proxy disclosure. See DIV-011.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>- **Anu Framework stage**: Stage 5 EXECUTION (Ch7 real-fix sub-stage); doctor gate IDs P13/P31/P36</t>
         </is>
       </c>
     </row>
@@ -1697,10 +2282,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -1755,7 +2340,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>PROXY CONSTRUCTION NOTICE</t>
+          <t>EXTENSION</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr"/>
@@ -1766,94 +2351,189 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>proxy</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>BLS+BEA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>proxy_basis</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>&lt;not specified&gt;</t>
+          <t>1977</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>proxy_disclosure</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Series is a proxy, not a direct replication. See DPR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+          <t>level</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>output_subseries</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>S701-EXT</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXTENSION</t>
+          <t>combined_subseries</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>null - series does not extend beyond book period</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>S701-COMBINED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>extension_period</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[1990, 2024]</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press., Chapter 7 (Table 7.1 (1947, 1958, 1963, 1967, 1972, 1977)).", "extension_source": "BLS CES production-worker hours + BEA gross output via the Ch4 \u00a74.1 sector formula hp*_j = (Lp_j * weekly_hours_j * 52) / X_j and the labeled BEA IO matrices", "note": "Extension block backfilled 2026-05-24 by doctor-cleanup pass to reflect actually-built extension data already present in chopped/&lt;sid&gt;.csv (validated_book_and_extension status). No substantive data change."}</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>reference_values</t>
+          <t>depends_on</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{"1947": 44.69718165489747, "1958": 18.399301852052265, "1963": 18.47703815217319, "1967": 2.079344184211604, "1972": 51.858541267564185, "1977": 51.71750101575981}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>expected_range</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>[1.0, 60.0]</t>
-        </is>
-      </c>
-    </row>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>{"1972": 18.45728, "1977": 10.692698, "2024": 27.722905}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>expected_range</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>[0.0164, 0.41]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>tolerance</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>hr_per_dollar</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Reference values now mirror the per-sector lambda_p = mean_j(hp*_j @ B) procedure in P02_S701 (v1.1 iter6). Book-period anchor years are the SIC IO benchmark years 1972 and 1977 (full BLS coverage of 69 productive sectors); pre-1972 years (1947, 1958, 1963, 1967) have thin BLS coverage and are not used as benchmarks. 2024 EXT endpoint added per Decision 0008.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>rate_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>extension_year_range</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>[1958, 2024]</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S701.xlsx
+++ b/extenbooks/S701.xlsx
@@ -447,13 +447,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
     <col width="41" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,6 +478,11 @@
           <t>BLS CES + BEA, units=hr_per_dollar</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BLS CES + rebuilt 1977 BEA I-O (A and nominal X both frozen), units=hr_per_dollar</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -497,6 +503,11 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>S701-EXT</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>S701-VAR-FROZEN77</t>
         </is>
       </c>
     </row>
@@ -505,12 +516,15 @@
         <v>1958</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.0050409664186513</v>
+        <v>0.1260823635190446</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.0050409664186513</v>
+        <v>0.1260823635190446</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E3" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -519,12 +533,15 @@
         <v>1963</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.0042927311714161</v>
+        <v>0.1039956210840949</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.0042927311714161</v>
+        <v>0.1039956210840949</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E4" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -533,12 +550,15 @@
         <v>1967</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.468706549340996</v>
+        <v>0.1641469546041618</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.468706549340996</v>
+        <v>0.1641469546041618</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E5" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -547,12 +567,15 @@
         <v>1972</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>18.45728042841037</v>
+        <v>0.095403076041572</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>18.45728042841037</v>
+        <v>0.095403076041572</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E6" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -561,12 +584,15 @@
         <v>1977</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>10.69269826800623</v>
+        <v>0.0608876539454238</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>10.69269826800623</v>
+        <v>0.0608876539454238</v>
       </c>
       <c r="D7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E7" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -578,10 +604,13 @@
         <v/>
       </c>
       <c r="C8" s="3" t="n">
-        <v>15.97122726515625</v>
+        <v>0.0255993558769199</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>15.97122726515625</v>
+        <v>0.0255993558769199</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.073907450801894</v>
       </c>
     </row>
     <row r="9">
@@ -592,10 +621,13 @@
         <v/>
       </c>
       <c r="C9" s="3" t="n">
-        <v>15.66039529373823</v>
+        <v>0.0247343686588675</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>15.66039529373823</v>
+        <v>0.0247343686588675</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0.0732216415906309</v>
       </c>
     </row>
     <row r="10">
@@ -606,10 +638,13 @@
         <v/>
       </c>
       <c r="C10" s="3" t="n">
-        <v>15.7097617488863</v>
+        <v>0.0236751534389642</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>15.7097617488863</v>
+        <v>0.0236751534389642</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.0740088580254662</v>
       </c>
     </row>
     <row r="11">
@@ -620,10 +655,13 @@
         <v/>
       </c>
       <c r="C11" s="3" t="n">
-        <v>16.17773750767611</v>
+        <v>0.0231842274492332</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>16.17773750767611</v>
+        <v>0.0231842274492332</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.07597138259559059</v>
       </c>
     </row>
     <row r="12">
@@ -634,10 +672,13 @@
         <v/>
       </c>
       <c r="C12" s="3" t="n">
-        <v>16.9307239740035</v>
+        <v>0.022452573842494</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>16.9307239740035</v>
+        <v>0.022452573842494</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.07884025061758169</v>
       </c>
     </row>
     <row r="13">
@@ -648,10 +689,13 @@
         <v/>
       </c>
       <c r="C13" s="3" t="n">
-        <v>17.55543945970671</v>
+        <v>0.0216077695286821</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>17.55543945970671</v>
+        <v>0.0216077695286821</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0.0806485860361765</v>
       </c>
     </row>
     <row r="14">
@@ -662,10 +706,13 @@
         <v/>
       </c>
       <c r="C14" s="3" t="n">
-        <v>18.13095167588034</v>
+        <v>0.0207715619900107</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>18.13095167588034</v>
+        <v>0.0207715619900107</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0.08207418072702451</v>
       </c>
     </row>
     <row r="15">
@@ -676,10 +723,13 @@
         <v/>
       </c>
       <c r="C15" s="3" t="n">
-        <v>18.83274660113012</v>
+        <v>0.0199832864761758</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>18.83274660113012</v>
+        <v>0.0199832864761758</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.0846377353807253</v>
       </c>
     </row>
     <row r="16">
@@ -690,10 +740,13 @@
         <v/>
       </c>
       <c r="C16" s="3" t="n">
-        <v>19.37170471226526</v>
+        <v>0.0195523794980985</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>19.37170471226526</v>
+        <v>0.0195523794980985</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0.0859959599022673</v>
       </c>
     </row>
     <row r="17">
@@ -704,10 +757,13 @@
         <v/>
       </c>
       <c r="C17" s="3" t="n">
-        <v>19.77247604050815</v>
+        <v>0.018658295302941</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>19.77247604050815</v>
+        <v>0.018658295302941</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0.0867002035188856</v>
       </c>
     </row>
     <row r="18">
@@ -718,10 +774,13 @@
         <v/>
       </c>
       <c r="C18" s="3" t="n">
-        <v>20.35657607411335</v>
+        <v>0.0175010195787817</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>20.35657607411335</v>
+        <v>0.0175010195787817</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0.0878487789364593</v>
       </c>
     </row>
     <row r="19">
@@ -732,10 +791,13 @@
         <v/>
       </c>
       <c r="C19" s="3" t="n">
-        <v>20.23955021370821</v>
+        <v>0.0169814385642684</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>20.23955021370821</v>
+        <v>0.0169814385642684</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0.0869216749937952</v>
       </c>
     </row>
     <row r="20">
@@ -746,10 +808,13 @@
         <v/>
       </c>
       <c r="C20" s="3" t="n">
-        <v>19.67443972775556</v>
+        <v>0.0158716398224715</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>19.67443972775556</v>
+        <v>0.0158716398224715</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.0856709658324764</v>
       </c>
     </row>
     <row r="21">
@@ -760,10 +825,13 @@
         <v/>
       </c>
       <c r="C21" s="3" t="n">
-        <v>19.39702298255986</v>
+        <v>0.0147940457349486</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>19.39702298255986</v>
+        <v>0.0147940457349486</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.0844980684941075</v>
       </c>
     </row>
     <row r="22">
@@ -774,10 +842,13 @@
         <v/>
       </c>
       <c r="C22" s="3" t="n">
-        <v>19.82560213432708</v>
+        <v>0.0139744375975309</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>19.82560213432708</v>
+        <v>0.0139744375975309</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0.0857730599501091</v>
       </c>
     </row>
     <row r="23">
@@ -788,10 +859,13 @@
         <v/>
       </c>
       <c r="C23" s="3" t="n">
-        <v>20.51991452680202</v>
+        <v>0.0131313816647243</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>20.51991452680202</v>
+        <v>0.0131313816647243</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0.0875713122913778</v>
       </c>
     </row>
     <row r="24">
@@ -802,10 +876,13 @@
         <v/>
       </c>
       <c r="C24" s="3" t="n">
-        <v>21.22474447817114</v>
+        <v>0.0125833427310918</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>21.22474447817114</v>
+        <v>0.0125833427310918</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0.0897641315717489</v>
       </c>
     </row>
     <row r="25">
@@ -816,10 +893,13 @@
         <v/>
       </c>
       <c r="C25" s="3" t="n">
-        <v>21.56722978432457</v>
+        <v>0.0123537805203684</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>21.56722978432457</v>
+        <v>0.0123537805203684</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.0911244328211073</v>
       </c>
     </row>
     <row r="26">
@@ -830,10 +910,13 @@
         <v/>
       </c>
       <c r="C26" s="3" t="n">
-        <v>21.40281376200356</v>
+        <v>0.0116790813695759</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>21.40281376200356</v>
+        <v>0.0116790813695759</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0.09095615382888229</v>
       </c>
     </row>
     <row r="27">
@@ -844,10 +927,13 @@
         <v/>
       </c>
       <c r="C27" s="3" t="n">
-        <v>19.5031283231772</v>
+        <v>0.0118911927442822</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>19.5031283231772</v>
+        <v>0.0118911927442822</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0.0860103040650648</v>
       </c>
     </row>
     <row r="28">
@@ -858,10 +944,13 @@
         <v/>
       </c>
       <c r="C28" s="3" t="n">
-        <v>19.26141680957129</v>
+        <v>0.0110908117575983</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>19.26141680957129</v>
+        <v>0.0110908117575983</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0.0864524534940528</v>
       </c>
     </row>
     <row r="29">
@@ -872,10 +961,13 @@
         <v/>
       </c>
       <c r="C29" s="3" t="n">
-        <v>19.91045826042743</v>
+        <v>0.0105492746158743</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>19.91045826042743</v>
+        <v>0.0105492746158743</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0.08851553596240409</v>
       </c>
     </row>
     <row r="30">
@@ -886,10 +978,13 @@
         <v/>
       </c>
       <c r="C30" s="3" t="n">
-        <v>20.53350665092178</v>
+        <v>0.0104478409444461</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>20.53350665092178</v>
+        <v>0.0104478409444461</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0.090791196298288</v>
       </c>
     </row>
     <row r="31">
@@ -900,10 +995,13 @@
         <v/>
       </c>
       <c r="C31" s="3" t="n">
-        <v>20.92768989475616</v>
+        <v>0.0102907276392995</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>20.92768989475616</v>
+        <v>0.0102907276392995</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0.0920475357948211</v>
       </c>
     </row>
     <row r="32">
@@ -914,10 +1012,13 @@
         <v/>
       </c>
       <c r="C32" s="3" t="n">
-        <v>21.58680728878629</v>
+        <v>0.0101038168082558</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>21.58680728878629</v>
+        <v>0.0101038168082558</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0.0939467632778699</v>
       </c>
     </row>
     <row r="33">
@@ -928,10 +1029,13 @@
         <v/>
       </c>
       <c r="C33" s="3" t="n">
-        <v>22.0995781999885</v>
+        <v>0.0103882582371973</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>22.0995781999885</v>
+        <v>0.0103882582371973</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0.09597458066763249</v>
       </c>
     </row>
     <row r="34">
@@ -942,10 +1046,13 @@
         <v/>
       </c>
       <c r="C34" s="3" t="n">
-        <v>22.39736987520822</v>
+        <v>0.010435111720538</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>22.39736987520822</v>
+        <v>0.010435111720538</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0.09755366723934419</v>
       </c>
     </row>
     <row r="35">
@@ -956,10 +1063,13 @@
         <v/>
       </c>
       <c r="C35" s="3" t="n">
-        <v>23.019440048035</v>
+        <v>0.009786893477124</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>23.019440048035</v>
+        <v>0.009786893477124</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0.0996403455173038</v>
       </c>
     </row>
     <row r="36">
@@ -970,10 +1080,13 @@
         <v/>
       </c>
       <c r="C36" s="3" t="n">
-        <v>23.92131857724761</v>
+        <v>0.0094359621446054</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>23.92131857724761</v>
+        <v>0.0094359621446054</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0.1020837752941722</v>
       </c>
     </row>
     <row r="37">
@@ -984,10 +1097,13 @@
         <v/>
       </c>
       <c r="C37" s="3" t="n">
-        <v>24.51718618172336</v>
+        <v>0.009322905723670401</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>24.51718618172336</v>
+        <v>0.009322905723670401</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0.1034304152140914</v>
       </c>
     </row>
     <row r="38">
@@ -998,10 +1114,13 @@
         <v/>
       </c>
       <c r="C38" s="3" t="n">
-        <v>22.54848498205374</v>
+        <v>0.0095082620493125</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>22.54848498205374</v>
+        <v>0.0095082620493125</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0.0965038110680663</v>
       </c>
     </row>
     <row r="39">
@@ -1012,10 +1131,13 @@
         <v/>
       </c>
       <c r="C39" s="3" t="n">
-        <v>23.84622962975419</v>
+        <v>0.0084959652636073</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>23.84622962975419</v>
+        <v>0.0084959652636073</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0.100100864013814</v>
       </c>
     </row>
     <row r="40">
@@ -1026,10 +1148,13 @@
         <v/>
       </c>
       <c r="C40" s="3" t="n">
-        <v>25.78432917817896</v>
+        <v>0.0077328828008668</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>25.78432917817896</v>
+        <v>0.0077328828008668</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0.1040754553538339</v>
       </c>
     </row>
     <row r="41">
@@ -1040,10 +1165,13 @@
         <v/>
       </c>
       <c r="C41" s="3" t="n">
-        <v>27.01540327503981</v>
+        <v>0.0076582608016077</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>27.01540327503981</v>
+        <v>0.0076582608016077</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0.1067649114028618</v>
       </c>
     </row>
     <row r="42">
@@ -1054,10 +1182,13 @@
         <v/>
       </c>
       <c r="C42" s="3" t="n">
-        <v>27.72290510895859</v>
+        <v>0.0073967922743262</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>27.72290510895859</v>
+        <v>0.0073967922743262</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0.1086823606418165</v>
       </c>
     </row>
   </sheetData>
@@ -1071,10 +1202,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B91"/>
+  <dimension ref="A1:B92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1283,52 +1414,56 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S701-VAR-FROZEN77</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BLS CES + rebuilt 1977 BEA I-O (A and nominal X both frozen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t># S701 — Labor Values (real, sector-disaggregated, hr/$)</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t># S701 — Labor Values (real, sector-disaggregated, hr/$)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>## Series</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>## Series</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>- **SID**: S701</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>- **Name**: Labor Values (Chapter 7 series; real implementation per Ch4 §4.1 formula)</t>
+          <t>- **SID**: S701</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1471,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>- **Chapter**: 7 (book §§7.1–7.5 magnitude framework); registry `book_table` label "7.1" is project-internal — the book's actual Table 7.1 is profit/accumulation/burden rates. The labor-value methodology lives in **Chapter 4 §4.1** (pp.78–88) and **Appendix G** (pp.304–322)</t>
+          <t>- **Name**: Labor Values (Chapter 7 series; real implementation per Ch4 §4.1 formula)</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1479,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>- **Status**: validated_book_and_extension</t>
+          <t>- **Chapter**: 7 (book §§7.1–7.5 magnitude framework); registry `book_table` label "7.1" is project-internal — the book's actual Table 7.1 is profit/accumulation/burden rates. The labor-value methodology lives in **Chapter 4 §4.1** (pp.78–88) and **Appendix G** (pp.304–322)</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1487,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>- **Status note**: (v1.1 Phase 4 — proxy:true retired)</t>
+          <t>- **Status**: validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -1360,63 +1495,63 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>- **Units**: hr/$ (labor-hours per dollar of producer-price gross output), per Ch4 §4.1 Figure 4.3 dimensional verification</t>
+          <t>- **Status note**: (v1.1 Phase 4 — proxy:true retired)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>- **Units**: hr/$ (labor-hours per dollar of producer-price gross output), per Ch4 §4.1 Figure 4.3 dimensional verification</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>## Methodology — real implementation (v1.1 Phase 4)</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>## Methodology — real implementation (v1.1 Phase 4)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>S701 implements the book's closed-form labor-value equation `lambda* = hp* * (I - A*)^{-1}` per ST 1994 Ch4 §4.1 (pp.80–83), where `hp*_j = hp_j / p_j` is the per-sector productive-labor-hours per dollar of producer-price gross output (hr/$). The v1.0 Leontief-column-mean proxy `mean(column_sum((I - A)^{-1}))` has been retired (DIV-011); the real implementation computes `hp*` directly from data.</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>S701 implements the book's closed-form labor-value equation `lambda* = hp* * (I - A*)^{-1}` per ST 1994 Ch4 §4.1 (pp.80–83), where `hp*_j = hp_j / p_j` is the per-sector productive-labor-hours per dollar of producer-price gross output (hr/$). The v1.0 Leontief-column-mean proxy `mean(column_sum((I - A)^{-1}))` has been retired (DIV-011); the real implementation computes `hp*` directly from data.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Formula (per `Technical/code/P02_processors/P02_S701_labor_values.py`, v1.1 rewrite):</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Formula (per `Technical/code/P02_processors/P02_S701_labor_values.py`, v1.1 rewrite):</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>hp*_j = (Lp_j * h_j * 52) / X_j        # hr/$ per productive sector j</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1559,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>lambda*_j = hp* * (I - A*_p)^{-1}      # hr/$ sector vector; A*_p = productive sub-matrix</t>
+          <t>hp*_j = (Lp_j * h_j * 52) / X_j        # hr/$ per productive sector j</t>
         </is>
       </c>
     </row>
@@ -1432,63 +1567,63 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>lambda*_j = hp* * (I - A*_p)^{-1}      # hr/$ sector vector; A*_p = productive sub-matrix</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>where `Lp_j` is BLS production-worker employment count per supersector (CES dataset), `h_j` is BLS average weekly hours per supersector, `X_j` is BEA producer-price gross output per sector (NIPA Table 1.7.5 SIC / GDP-by-Industry NAICS), and `(I - A*_p)^{-1}` is the Leontief inverse of the productive sub-matrix from labeled BEA benchmark IO tables filtered by the Appendix F productive-share mask. Sector aggregation follows the 8 ST productive sectors enumerated in Appendix G Table G.2 (agriculture, mining, construction, manufacturing, transportation &amp; public utilities, productive services, government enterprises federal, government enterprises state-local).</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>where `Lp_j` is BLS production-worker employment count per supersector (CES dataset), `h_j` is BLS average weekly hours per supersector, `X_j` is BEA producer-price gross output per sector (NIPA Table 1.7.5 SIC / GDP-by-Industry NAICS), and `(I - A*_p)^{-1}` is the Leontief inverse of the productive sub-matrix from labeled BEA benchmark IO tables filtered by the Appendix F productive-share mask. Sector aggregation follows the 8 ST productive sectors enumerated in Appendix G Table G.2 (agriculture, mining, construction, manufacturing, transportation &amp; public utilities, productive services, government enterprises federal, government enterprises state-local).</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>The book's dimensional verification (Figure 4.3 p.83) — `lambda* = TV / GO_p` in hr/$ — is satisfied by construction for the first time in v1.1; the v1.0 proxy could not perform this check because it omitted `hp*` entirely.</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>The book's dimensional verification (Figure 4.3 p.83) — `lambda* = TV / GO_p` in hr/$ — is satisfied by construction for the first time in v1.1; the v1.0 proxy could not perform this check because it omitted `hp*` entirely.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>## Sources</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>## Sources</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>- **L01 + P02 (real implementation)**: `Technical/code/L01_loaders/L01_S701.py` (v1.1, loads BLS CES + BEA gross output + labeled IO matrices + Appendix F filter); `Technical/code/P02_processors/P02_S701_labor_values.py` (v1.1 rewrite, applies hp* formula then Leontief inverse on productive sub-matrix)</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>- **External data — real fetches**:</t>
+          <t>- **L01 + P02 (real implementation)**: `Technical/code/L01_loaders/L01_S701.py` (v1.1, loads BLS CES + BEA gross output + labeled IO matrices + Appendix F filter); `Technical/code/P02_processors/P02_S701_labor_values.py` (v1.1 rewrite, applies hp* formula then Leontief inverse on productive sub-matrix)</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1631,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - BLS CES production workers + weekly hours, cached at `Inputs/ST2/Inputs/API_Data/BLS/bls_ces_&lt;supersector&gt;_employment.csv` and `_hours.csv` / `_hours_alt.csv` (pulled 2026-05-24 via `Technical/code/L00_setup/L00_bls_fetch.py`; provenance at `bls_ces_fetch_provenance.json`)</t>
+          <t>- **External data — real fetches**:</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1639,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - BEA gross output, cached at `Inputs/ST2/Inputs/API_Data/BEA/nipa_1_7_5_gross_output_by_industry.csv` + `gdp_by_industry_gross_output.csv` (pulled 2026-02-24; provenance at `Inputs/ST2/Inputs/API_Data/BEA/provenance.json`)</t>
+          <t xml:space="preserve">  - BLS CES production workers + weekly hours, cached at `Inputs/ST2/Inputs/API_Data/BLS/bls_ces_&lt;supersector&gt;_employment.csv` and `_hours.csv` / `_hours_alt.csv` (pulled 2026-05-24 via `Technical/code/L00_setup/L00_bls_fetch.py`; provenance at `bls_ces_fetch_provenance.json`)</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1647,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Labeled BEA IO matrices, cached at `Technical/data/intermediate/io_matrices_labeled/` (from `Inputs/ST2/Inputs/IO_Matrices/`)</t>
+          <t xml:space="preserve">  - BEA gross output, cached at `Inputs/ST2/Inputs/API_Data/BEA/nipa_1_7_5_gross_output_by_industry.csv` + `gdp_by_industry_gross_output.csv` (pulled 2026-02-24; provenance at `Inputs/ST2/Inputs/API_Data/BEA/provenance.json`)</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1655,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Appendix F productive-share filter, at `Technical/data/source/appendix_F/Table_F_1.csv` (85-sector categorical mask, derived from ST2 `io_85_to_nipa_13_concordance.csv` + Mohun 2013 Tables 2-3, provenance at `Technical/data/source/appendix_F/PROVENANCE.md`)</t>
+          <t xml:space="preserve">  - Labeled BEA IO matrices, cached at `Technical/data/intermediate/io_matrices_labeled/` (from `Inputs/ST2/Inputs/IO_Matrices/`)</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1663,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>- **KB chunks**: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_11/full_transcription.md` (Ch4 §4.1 pp.78-83 — closed-form equations + Figure 4.3); `chunk_14/full_transcription.md` (Appendix G variable capital); `chunk_15/full_transcription.md` (sector composition); `chunk_31/full_transcription.md` (Appendix E sectoral GVAp); `chunk_33/full_transcription.md` (Appendix F + G intro)</t>
+          <t xml:space="preserve">  - Appendix F productive-share filter, at `Technical/data/source/appendix_F/Table_F_1.csv` (85-sector categorical mask, derived from ST2 `io_85_to_nipa_13_concordance.csv` + Mohun 2013 Tables 2-3, provenance at `Technical/data/source/appendix_F/PROVENANCE.md`)</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1671,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>- **Book tables**: Ch4 §4.1 equations pp.80-83 (Figure 4.3 dimensional check); Appendix G Table G.2 (sectoral productive employment); Appendix F (productive shares — book's annual labor decomposition pp.292–301); Appendix E Tables E.1 / E.2</t>
+          <t>- **KB chunks**: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_11/full_transcription.md` (Ch4 §4.1 pp.78-83 — closed-form equations + Figure 4.3); `chunk_14/full_transcription.md` (Appendix G variable capital); `chunk_15/full_transcription.md` (sector composition); `chunk_31/full_transcription.md` (Appendix E sectoral GVAp); `chunk_33/full_transcription.md` (Appendix F + G intro)</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1679,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>- **APIs**: BLS Public API v2 (free registration key, supplied via the `BLS_API_KEY` environment variable); BEA API</t>
+          <t>- **Book tables**: Ch4 §4.1 equations pp.80-83 (Figure 4.3 dimensional check); Appendix G Table G.2 (sectoral productive employment); Appendix F (productive shares — book's annual labor decomposition pp.292–301); Appendix E Tables E.1 / E.2</t>
         </is>
       </c>
     </row>
@@ -1552,51 +1687,51 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>- **Upstream series**: S401 (A-matrix), S402 (Leontief inverse B), S513 (Marxian profit rate, used in downstream S702/S703)</t>
+          <t>- **APIs**: BLS Public API v2 (free registration key, supplied via the `BLS_API_KEY` environment variable); BEA API</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>- **Upstream series**: S401 (A-matrix), S402 (Leontief inverse B), S513 (Marxian profit rate, used in downstream S702/S703)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>## Reference values</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>## Reference values</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Coordinator backfills from `Technical/chopped/S701.csv` after agents 1-3 commit L01/P02 rewrites and `O01_generate_chopped.py` regenerates the chopped output. Expected magnitude: O(0.1–10) hr/$ per sector; book Figure 4.3 worked-case anchor is 2 hr/$ for a single-sector toy economy.</t>
-        </is>
-      </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Coordinator backfills from `Technical/chopped/S701.csv` after agents 1-3 commit L01/P02 rewrites and `O01_generate_chopped.py` regenerates the chopped output. Expected magnitude: O(0.1–10) hr/$ per sector; book Figure 4.3 worked-case anchor is 2 hr/$ for a single-sector toy economy.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>- Six SIC benchmark years (book period): 1947, 1958, 1963, 1967, 1972, 1977</t>
-        </is>
-      </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>- Extension years (NAICS basis): 1997, 2002, 2007, 2012 (per BEA benchmark IO availability)</t>
+          <t>- Six SIC benchmark years (book period): 1947, 1958, 1963, 1967, 1972, 1977</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1739,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>- Book's qualitative magnitude framework (Ch7 §7.3 p.221): **"Marxian total product TP* is roughly 82% of the IO measure of gross product GP, but about 1.5 times larger than the conventional measure of GNP."** S701 lambda* aggregates feed this framework via downstream Ch7 series.</t>
+          <t>- Extension years (NAICS basis): 1997, 2002, 2007, 2012 (per BEA benchmark IO availability)</t>
         </is>
       </c>
     </row>
@@ -1612,39 +1747,39 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>- Dimensional verification (Figure 4.3 p.83): `lambda* = TV / GO_p` in hr/$ — satisfied by construction in v1.1, was unsatisfiable in v1.0 proxy.</t>
+          <t>- Book's qualitative magnitude framework (Ch7 §7.3 p.221): **"Marxian total product TP* is roughly 82% of the IO measure of gross product GP, but about 1.5 times larger than the conventional measure of GNP."** S701 lambda* aggregates feed this framework via downstream Ch7 series.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>- Dimensional verification (Figure 4.3 p.83): `lambda* = TV / GO_p` in hr/$ — satisfied by construction in v1.1, was unsatisfiable in v1.0 proxy.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>## Known issues</t>
-        </is>
-      </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>## Known issues</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>- **BLS CES 2003 overhaul null bridge (DIV-010)**: v1.1 ships factor=1.0 stubs per supersector; non-null factors deferred to v1.2 (BLS Employment Situation news-release archive sourcing). Effect: intra-extension trend from 2003 onward may carry minor methodology-break artifacts; the 1989 SIC↔NAICS anchor reconciliation remains the dominant cross-period level adjustment.</t>
-        </is>
-      </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>- **SIC↔NAICS coarse concordance** (post-1997 sector mapping; DIV-008 reference): productive-classification mapping book ↔ extension is at supersector granularity; finer-grained sector reassignments not yet handled.</t>
+          <t>- **BLS CES 2003 overhaul null bridge (DIV-010)**: v1.1 ships factor=1.0 stubs per supersector; non-null factors deferred to v1.2 (BLS Employment Situation news-release archive sourcing). Effect: intra-extension trend from 2003 onward may carry minor methodology-break artifacts; the 1989 SIC↔NAICS anchor reconciliation remains the dominant cross-period level adjustment.</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1787,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>- **1963 benchmark anomaly (WARN-03)**: v1.0 proxy showed S701 = 0.00037 at 1963 (likely IO data gap); v1.1 real implementation may inherit if the gap is in the underlying labeled IO matrix. If V03 surfaces it, document as known_issue rather than re-introducing proxy.</t>
+          <t>- **SIC↔NAICS coarse concordance** (post-1997 sector mapping; DIV-008 reference): productive-classification mapping book ↔ extension is at supersector granularity; finer-grained sector reassignments not yet handled.</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1795,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>- **Services sector compensation proxy**: per ST methodology, average compensation `ec_serv` is used as a stand-in for `(ecp)_serv` because BLS production-wage data are unavailable for services. Documented in Appendix G; preserved in v1.1 real implementation.</t>
+          <t>- **1963 benchmark anomaly (WARN-03)**: v1.0 proxy showed S701 = 0.00037 at 1963 (likely IO data gap); v1.1 real implementation may inherit if the gap is in the underlying labeled IO matrix. If V03 surfaces it, document as known_issue rather than re-introducing proxy.</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1803,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>- **Agriculture productive-employment proxy**: ST uses mining-sector Lp/L ratio for agriculture (own BLS production-worker data unavailable). Preserved in v1.1.</t>
+          <t>- **Services sector compensation proxy**: per ST methodology, average compensation `ec_serv` is used as a stand-in for `(ecp)_serv` because BLS production-wage data are unavailable for services. Documented in Appendix G; preserved in v1.1 real implementation.</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1811,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>- **Appendix F filter is categorical**: the 85-sector productive/unproductive mask in `Technical/data/source/appendix_F/Table_F_1.csv` is binary (productive=1.0, unproductive=0.0, plus 3 uncertain sectors flagged) rather than fractional. The per-sector fractional shares the user originally envisioned do not literally exist as a published table; within-sector productive ratios are applied at compute time via BLS production-worker series per ST/Mohun methodology.</t>
+          <t>- **Agriculture productive-employment proxy**: ST uses mining-sector Lp/L ratio for agriculture (own BLS production-worker data unavailable). Preserved in v1.1.</t>
         </is>
       </c>
     </row>
@@ -1684,39 +1819,39 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>- **Six SIC benchmark years only** for book period; no annual interpolation within the book period.</t>
+          <t>- **Appendix F filter is categorical**: the 85-sector productive/unproductive mask in `Technical/data/source/appendix_F/Table_F_1.csv` is binary (productive=1.0, unproductive=0.0, plus 3 uncertain sectors flagged) rather than fractional. The per-sector fractional shares the user originally envisioned do not literally exist as a published table; within-sector productive ratios are applied at compute time via BLS production-worker series per ST/Mohun methodology.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>- **Six SIC benchmark years only** for book period; no annual interpolation within the book period.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>## Cross-references</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>## Cross-references</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>- Upstream: S401 (A-matrix), S402 (Leontief inverse B), Appendix F productive-share filter, Appendix G Table G.2 (sectoral productive employment), BLS CES, BEA NIPA 1.7.5 / GDP-by-Industry</t>
-        </is>
-      </c>
+      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>- Downstream: S702 (prices of production, now also real and sector-disaggregated), S703 (consistent-procedure regression)</t>
+          <t>- Upstream: S401 (A-matrix), S402 (Leontief inverse B), Appendix F productive-share filter, Appendix G Table G.2 (sectoral productive employment), BLS CES, BEA NIPA 1.7.5 / GDP-by-Industry</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1859,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>- Related external: Wolff (1977b) symmetric-treatment biases S*/V* upward 4–8%; Khanjian (1989) consistent procedure 6–9% S*/V* deviation; ST 1994 Ch7 §7.4 cross-study critique</t>
+          <t>- Downstream: S702 (prices of production, now also real and sector-disaggregated), S703 (consistent-procedure regression)</t>
         </is>
       </c>
     </row>
@@ -1732,39 +1867,39 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>- Project artifacts: `Technical/Handoffs/CH7_REAL_FIX_PLAN.md`; `Technical/_v1.1_patches/S701_ch7_realfix_patch.json`; `Technical/_v1.1_patches/DIVERGENCE_REGISTER_DIV011_patch.json`</t>
+          <t>- Related external: Wolff (1977b) symmetric-treatment biases S*/V* upward 4–8%; Khanjian (1989) consistent procedure 6–9% S*/V* deviation; ST 1994 Ch7 §7.4 cross-study critique</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>- Project artifacts: `Technical/Handoffs/CH7_REAL_FIX_PLAN.md`; `Technical/_v1.1_patches/S701_ch7_realfix_patch.json`; `Technical/_v1.1_patches/DIVERGENCE_REGISTER_DIV011_patch.json`</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>## Provenance trail</t>
-        </is>
-      </c>
+      <c r="B86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>## Provenance trail</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>- **Original research**: `Technical/research/S701_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T701_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23 (Stage 1 cohort 3 enrichment specifically anchored Ch4 §4.1 equations + Figure 4.3 dimensional check)</t>
-        </is>
-      </c>
+      <c r="B88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>- **DPR v1.0**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (proxy disclosure version)</t>
+          <t>- **Original research**: `Technical/research/S701_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T701_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23 (Stage 1 cohort 3 enrichment specifically anchored Ch4 §4.1 equations + Figure 4.3 dimensional check)</t>
         </is>
       </c>
     </row>
@@ -1772,13 +1907,21 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>- **DPR v1.1 (this version)**: 2026-05-24, v1.1 Phase 4 iteration 5 Ch7 real-fix agent 4 (registry/DPR/EPR cohort, parallel to agents 1-3 doing L01/P02 rewrites). Real implementation replaces proxy disclosure. See DIV-011.</t>
+          <t>- **DPR v1.0**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (proxy disclosure version)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
+        <is>
+          <t>- **DPR v1.1 (this version)**: 2026-05-24, v1.1 Phase 4 iteration 5 Ch7 real-fix agent 4 (registry/DPR/EPR cohort, parallel to agents 1-3 doing L01/P02 rewrites). Real implementation replaces proxy disclosure. See DIV-011.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
         <is>
           <t>- **Anu Framework stage**: Stage 5 EXECUTION (Ch7 real-fix sub-stage); doctor gate IDs P13/P31/P36</t>
         </is>
@@ -2368,7 +2511,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>1997</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2523,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>ratio (1997 both-ways overlap; factor 1.173491 = sic_path 0.019983 / naics_path 0.017029)</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2571,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press., Chapter 7 (Table 7.1 (1947, 1958, 1963, 1967, 1972, 1977)).", "extension_source": "BLS CES production-worker hours + BEA gross output via the Ch4 \u00a74.1 sector formula hp*_j = (Lp_j * weekly_hours_j * 52) / X_j and the labeled BEA IO matrices", "note": "Extension block backfilled 2026-05-24 by doctor-cleanup pass to reflect actually-built extension data already present in chopped/&lt;sid&gt;.csv (validated_book_and_extension status). No substantive data change."}</t>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press., Chapter 7 (Table 7.1 (1947, 1958, 1963, 1967, 1972, 1977)).", "extension_source": "Moving-benchmark extension (P2_FROZEN_WEIGHTS_AUDIT recommendation): 1990-96 rebuilt-1977 SIC A with X_j updated annually from BEA SIC-era GDP-by-industry VA growth (GDPbyInd_VA_SIC.xls); 1997-2024 nearest-previous NAICS benchmark Total Requirements (1997/2002/2007/2012/2017) with annual BEA gross output and SIC-&gt;NAICS bridge hour remap; 1997 break ratio-spliced (documented method change).", "note": "Extension block backfilled 2026-05-24 by doctor-cleanup pass to reflect actually-built extension data already present in chopped/&lt;sid&gt;.csv (validated_book_and_extension status). No substantive data change."}</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2604,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{"1972": 18.45728, "1977": 10.692698, "2024": 27.722905}</t>
+          <t>{"1958": 0.126082, "1977": 0.060888, "1990": 0.025599, "2024": 0.007397}</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2616,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[0.0164, 0.41]</t>
+          <t>[0.001, 1.0]</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2652,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Reference values now mirror the per-sector lambda_p = mean_j(hp*_j @ B) procedure in P02_S701 (v1.1 iter6). Book-period anchor years are the SIC IO benchmark years 1972 and 1977 (full BLS coverage of 69 productive sectors); pre-1972 years (1947, 1958, 1963, 1967) have thin BLS coverage and are not used as benchmarks. 2024 EXT endpoint added per Decision 0008.</t>
+          <t>Pipeline regression snapshot on the REBUILT matrix cache + corrected hours (WP-C v2.0). NO book numeric anchor exists: the book prints no lambda table (Ch7 has only Table 7.1 profit/burden rates; Ch4 4.1-4.4 are formulas/toy examples; Appendix G is money wages — v2 KB verified 2026-07-01). Values are hours per CURRENT-year nominal dollar, hence declining.</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S701.xlsx
+++ b/extenbooks/S701.xlsx
@@ -1639,7 +1639,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - BLS CES production workers + weekly hours, cached at `Inputs/ST2/Inputs/API_Data/BLS/bls_ces_&lt;supersector&gt;_employment.csv` and `_hours.csv` / `_hours_alt.csv` (pulled 2026-05-24 via `Technical/code/L00_setup/L00_bls_fetch.py`; provenance at `bls_ces_fetch_provenance.json`)</t>
+          <t xml:space="preserve">  - BLS CES production workers + weekly hours, cached at `data/raw/Inputs/API_Data/BLS/bls_ces_&lt;supersector&gt;_employment.csv` and `_hours.csv` / `_hours_alt.csv` (pulled 2026-05-24 via `Technical/code/L00_setup/L00_bls_fetch.py`; provenance at `bls_ces_fetch_provenance.json`)</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - BEA gross output, cached at `Inputs/ST2/Inputs/API_Data/BEA/nipa_1_7_5_gross_output_by_industry.csv` + `gdp_by_industry_gross_output.csv` (pulled 2026-02-24; provenance at `Inputs/ST2/Inputs/API_Data/BEA/provenance.json`)</t>
+          <t xml:space="preserve">  - BEA gross output, cached at `data/raw/Inputs/API_Data/BEA/nipa_1_7_5_gross_output_by_industry.csv` + `gdp_by_industry_gross_output.csv` (pulled 2026-02-24; provenance at `data/raw/Inputs/API_Data/BEA/provenance.json`)</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Labeled BEA IO matrices, cached at `Technical/data/intermediate/io_matrices_labeled/` (from `Inputs/ST2/Inputs/IO_Matrices/`)</t>
+          <t xml:space="preserve">  - Labeled BEA IO matrices, cached at `Technical/data/intermediate/io_matrices_labeled/` (from `data/raw/Inputs/IO_Matrices/`)</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Appendix F productive-share filter, at `Technical/data/source/appendix_F/Table_F_1.csv` (85-sector categorical mask, derived from ST2 `io_85_to_nipa_13_concordance.csv` + Mohun 2013 Tables 2-3, provenance at `Technical/data/source/appendix_F/PROVENANCE.md`)</t>
+          <t xml:space="preserve">  - Appendix F productive-share filter, at `Technical/data/source/appendix_F/Table_F_1.csv` (85-sector categorical mask, derived from predecessor-build `io_85_to_nipa_13_concordance.csv` + Mohun 2013 Tables 2-3, provenance at `Technical/data/source/appendix_F/PROVENANCE.md`)</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>- **Original research**: `Technical/research/S701_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T701_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23 (Stage 1 cohort 3 enrichment specifically anchored Ch4 §4.1 equations + Figure 4.3 dimensional check)</t>
+          <t>- **Original research**: `Technical/research/S701_research.json`, researcher `agent`, 2026-05-06; ported from `predecessor-build/research/T701_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23 (Stage 1 cohort 3 enrichment specifically anchored Ch4 §4.1 equations + Figure 4.3 dimensional check)</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[internal-decision-record] documents that the initial ST2 implementation of S701-derived labor values produced R² = 0.003–0.035 in the S703 regression (vs. book claim R² &gt; 0.95). Part of this failure traces to the S701–S702 interface: labor values λ_j (hours per dollar) must be converted to commensurable units before regression using the scalar λ_m = H_p / VA*. The 1963 benchmark year shows a data discontinuity (S701 drops to 0.00037 at 1963 before jumping to 0.036 in 1964), designated WARN-03, likely reflecting a gap in the underlying 1963 BEA IO table rather than a real economic break. The six-benchmark-year design of S701 (1947, 1958, 1963, 1967, 1972, 1977) means it is a cross-sectional series with no annual interpolation and no NAICS-era extension planned.</t>
+          <t>[internal-decision-record] documents that the initial predecessor-build implementation of S701-derived labor values produced R² = 0.003–0.035 in the S703 regression (vs. book claim R² &gt; 0.95). Part of this failure traces to the S701–S702 interface: labor values λ_j (hours per dollar) must be converted to commensurable units before regression using the scalar λ_m = H_p / VA*. The 1963 benchmark year shows a data discontinuity (S701 drops to 0.00037 at 1963 before jumping to 0.036 in 1964), designated WARN-03, likely reflecting a gap in the underlying 1963 BEA IO table rather than a real economic break. The six-benchmark-year design of S701 (1947, 1958, 1963, 1967, 1972, 1977) means it is a cross-sectional series with no annual interpolation and no NAICS-era extension planned.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2314,7 +2314,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>λ_m scalar conversion required before S701 can be regressed against S702 in S703; initial ST2 implementation omitted this step (see [internal-decision-record])</t>
+          <t>λ_m scalar conversion required before S701 can be regressed against S702 in S703; initial predecessor-build implementation omitted this step (see [internal-decision-record])</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S701.xlsx
+++ b/extenbooks/S701.xlsx
@@ -516,10 +516,10 @@
         <v>1958</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.1260823635190446</v>
+        <v>0.126</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.1260823635190446</v>
+        <v>0.126</v>
       </c>
       <c r="D3" s="3" t="n">
         <v/>
@@ -533,10 +533,10 @@
         <v>1963</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.1039956210840949</v>
+        <v>0.104</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.1039956210840949</v>
+        <v>0.104</v>
       </c>
       <c r="D4" s="3" t="n">
         <v/>
@@ -550,10 +550,10 @@
         <v>1967</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.1641469546041618</v>
+        <v>0.164</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.1641469546041618</v>
+        <v>0.164</v>
       </c>
       <c r="D5" s="3" t="n">
         <v/>
@@ -567,10 +567,10 @@
         <v>1972</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.095403076041572</v>
+        <v>0.0954</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.095403076041572</v>
+        <v>0.0954</v>
       </c>
       <c r="D6" s="3" t="n">
         <v/>
@@ -584,10 +584,10 @@
         <v>1977</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.0608876539454238</v>
+        <v>0.0609</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.0608876539454238</v>
+        <v>0.0609</v>
       </c>
       <c r="D7" s="3" t="n">
         <v/>
@@ -604,13 +604,13 @@
         <v/>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.0255993558769199</v>
+        <v>0.0256</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.0255993558769199</v>
+        <v>0.0256</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.073907450801894</v>
+        <v>0.07389999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -621,13 +621,13 @@
         <v/>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.0247343686588675</v>
+        <v>0.0247</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.0247343686588675</v>
+        <v>0.0247</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.0732216415906309</v>
+        <v>0.0732</v>
       </c>
     </row>
     <row r="10">
@@ -638,13 +638,13 @@
         <v/>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.0236751534389642</v>
+        <v>0.0237</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.0236751534389642</v>
+        <v>0.0237</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.0740088580254662</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="11">
@@ -655,13 +655,13 @@
         <v/>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.0231842274492332</v>
+        <v>0.0232</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.0231842274492332</v>
+        <v>0.0232</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.07597138259559059</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="12">
@@ -672,13 +672,13 @@
         <v/>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.022452573842494</v>
+        <v>0.0225</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.022452573842494</v>
+        <v>0.0225</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.07884025061758169</v>
+        <v>0.0788</v>
       </c>
     </row>
     <row r="13">
@@ -689,13 +689,13 @@
         <v/>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.0216077695286821</v>
+        <v>0.0216</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.0216077695286821</v>
+        <v>0.0216</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.0806485860361765</v>
+        <v>0.0806</v>
       </c>
     </row>
     <row r="14">
@@ -706,13 +706,13 @@
         <v/>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.0207715619900107</v>
+        <v>0.0208</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.0207715619900107</v>
+        <v>0.0208</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.08207418072702451</v>
+        <v>0.08210000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -723,13 +723,13 @@
         <v/>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.0199832864761758</v>
+        <v>0.02</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.0199832864761758</v>
+        <v>0.02</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.0846377353807253</v>
+        <v>0.08459999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -740,13 +740,13 @@
         <v/>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.0195523794980985</v>
+        <v>0.0196</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.0195523794980985</v>
+        <v>0.0196</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.0859959599022673</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -757,13 +757,13 @@
         <v/>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.018658295302941</v>
+        <v>0.0187</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.018658295302941</v>
+        <v>0.0187</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.0867002035188856</v>
+        <v>0.0867</v>
       </c>
     </row>
     <row r="18">
@@ -774,13 +774,13 @@
         <v/>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.0175010195787817</v>
+        <v>0.0175</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.0175010195787817</v>
+        <v>0.0175</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.0878487789364593</v>
+        <v>0.0878</v>
       </c>
     </row>
     <row r="19">
@@ -791,13 +791,13 @@
         <v/>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.0169814385642684</v>
+        <v>0.017</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.0169814385642684</v>
+        <v>0.017</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.0869216749937952</v>
+        <v>0.08690000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -808,13 +808,13 @@
         <v/>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.0158716398224715</v>
+        <v>0.0159</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.0158716398224715</v>
+        <v>0.0159</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.0856709658324764</v>
+        <v>0.0857</v>
       </c>
     </row>
     <row r="21">
@@ -825,13 +825,13 @@
         <v/>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.0147940457349486</v>
+        <v>0.0148</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.0147940457349486</v>
+        <v>0.0148</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.0844980684941075</v>
+        <v>0.08450000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -842,13 +842,13 @@
         <v/>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.0139744375975309</v>
+        <v>0.014</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.0139744375975309</v>
+        <v>0.014</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0.0857730599501091</v>
+        <v>0.0858</v>
       </c>
     </row>
     <row r="23">
@@ -859,13 +859,13 @@
         <v/>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.0131313816647243</v>
+        <v>0.0131</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.0131313816647243</v>
+        <v>0.0131</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.0875713122913778</v>
+        <v>0.0876</v>
       </c>
     </row>
     <row r="24">
@@ -876,13 +876,13 @@
         <v/>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.0125833427310918</v>
+        <v>0.0126</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.0125833427310918</v>
+        <v>0.0126</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.0897641315717489</v>
+        <v>0.0898</v>
       </c>
     </row>
     <row r="25">
@@ -893,13 +893,13 @@
         <v/>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0.0123537805203684</v>
+        <v>0.0124</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.0123537805203684</v>
+        <v>0.0124</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.0911244328211073</v>
+        <v>0.0911</v>
       </c>
     </row>
     <row r="26">
@@ -910,13 +910,13 @@
         <v/>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.0116790813695759</v>
+        <v>0.0117</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.0116790813695759</v>
+        <v>0.0117</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.09095615382888229</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="27">
@@ -927,13 +927,13 @@
         <v/>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.0118911927442822</v>
+        <v>0.0119</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.0118911927442822</v>
+        <v>0.0119</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.0860103040650648</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -944,13 +944,13 @@
         <v/>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.0110908117575983</v>
+        <v>0.0111</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.0110908117575983</v>
+        <v>0.0111</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.0864524534940528</v>
+        <v>0.08649999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -961,13 +961,13 @@
         <v/>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.0105492746158743</v>
+        <v>0.0105</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.0105492746158743</v>
+        <v>0.0105</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.08851553596240409</v>
+        <v>0.0885</v>
       </c>
     </row>
     <row r="30">
@@ -978,13 +978,13 @@
         <v/>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.0104478409444461</v>
+        <v>0.0104</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.0104478409444461</v>
+        <v>0.0104</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.090791196298288</v>
+        <v>0.09080000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -995,13 +995,13 @@
         <v/>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.0102907276392995</v>
+        <v>0.0103</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.0102907276392995</v>
+        <v>0.0103</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.0920475357948211</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="32">
@@ -1012,13 +1012,13 @@
         <v/>
       </c>
       <c r="C32" s="3" t="n">
-        <v>0.0101038168082558</v>
+        <v>0.0101</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.0101038168082558</v>
+        <v>0.0101</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>0.0939467632778699</v>
+        <v>0.0939</v>
       </c>
     </row>
     <row r="33">
@@ -1029,13 +1029,13 @@
         <v/>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.0103882582371973</v>
+        <v>0.0104</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.0103882582371973</v>
+        <v>0.0104</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0.09597458066763249</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="34">
@@ -1046,13 +1046,13 @@
         <v/>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.010435111720538</v>
+        <v>0.0104</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.010435111720538</v>
+        <v>0.0104</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.09755366723934419</v>
+        <v>0.09760000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1063,13 +1063,13 @@
         <v/>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0.009786893477124</v>
+        <v>0.00979</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0.009786893477124</v>
+        <v>0.00979</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0.0996403455173038</v>
+        <v>0.09959999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1080,13 +1080,13 @@
         <v/>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.0094359621446054</v>
+        <v>0.00944</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.0094359621446054</v>
+        <v>0.00944</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.1020837752941722</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="37">
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0.009322905723670401</v>
+        <v>0.00932</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.009322905723670401</v>
+        <v>0.00932</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0.1034304152140914</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="38">
@@ -1114,13 +1114,13 @@
         <v/>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0.0095082620493125</v>
+        <v>0.009509999999999999</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0.0095082620493125</v>
+        <v>0.009509999999999999</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0.0965038110680663</v>
+        <v>0.0965</v>
       </c>
     </row>
     <row r="39">
@@ -1131,13 +1131,13 @@
         <v/>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0.0084959652636073</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0.0084959652636073</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>0.100100864013814</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="40">
@@ -1148,13 +1148,13 @@
         <v/>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.0077328828008668</v>
+        <v>0.00773</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0.0077328828008668</v>
+        <v>0.00773</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0.1040754553538339</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="41">
@@ -1165,13 +1165,13 @@
         <v/>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.0076582608016077</v>
+        <v>0.00766</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.0076582608016077</v>
+        <v>0.00766</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.1067649114028618</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="42">
@@ -1182,13 +1182,13 @@
         <v/>
       </c>
       <c r="C42" s="3" t="n">
-        <v>0.0073967922743262</v>
+        <v>0.0074</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>0.0073967922743262</v>
+        <v>0.0074</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>0.1086823606418165</v>
+        <v>0.109</v>
       </c>
     </row>
   </sheetData>
@@ -1202,7 +1202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B92"/>
+  <dimension ref="A1:B96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1655,7 +1655,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Labeled BEA IO matrices, cached at `Technical/data/intermediate/io_matrices_labeled/` (from `data/raw/Inputs/IO_Matrices/`)</t>
+          <t xml:space="preserve">  - BEA IO matrices. **[SUPERSEDED — WP-C v2.0 / F3 2026-07-07]** the published v2.0 engine reads the REBUILT cache `Technical/data/intermediate/io_matrices_rebuilt/` (via `utils.io_rebuilt`); the old defective labeled cache was retired to `Technical/MIGRATION/retired_io_20260707/io_matrices_labeled/` (see its RETIRE_NOTE.md). Historical original: labeled cache from `data/raw/Inputs/IO_Matrices/`.</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>## Known issues</t>
+          <t>## Precision &amp; uncertainty (DIV-042) — Tier-A W1d, 2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1779,39 +1779,31 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>- **BLS CES 2003 overhaul null bridge (DIV-010)**: v1.1 ships factor=1.0 stubs per supersector; non-null factors deferred to v1.2 (BLS Employment Situation news-release archive sourcing). Effect: intra-extension trend from 2003 onward may carry minor methodology-break artifacts; the 1989 SIC↔NAICS anchor reconciliation remains the dominant cross-period level adjustment.</t>
+          <t>Published S701 values (`data/final/S701.csv`, `chopped/S701.csv`, extenbook Data sheet) are reported to **3 significant figures** with an explicit uncertainty-band sidecar at `data/final/S701_LAMBDA_BAND.csv` (year, central, lo, hi, basis). Basis: **DIV-042** — the SIC-era per-sector gross output X_j entering both the hours-allocation weights and the coefficient denominator `hp*_j = hp_j/X_j` is *recovered* (X = II_IO + bucket-VA) with a measured median per-sector error of ~±11.5%. The F3 sensitivity propagation (`Handoffs/REVIEW_2026-07-07/F3_lambda_sensitivity_{aggregate,sector}.csv`, 2026-07-07) shows the published aggregate is honest only to ±2.7–4.3% (independent-error Monte Carlo) up to ±11.65% (worst-case common-mode); sector-level λ_j carries ±7–11%. The previous 15–17 displayed digits were false precision. The band uses the worst-case common-mode bound: `lo = central/1.115`, `hi = central/0.885` (λ ∝ 1/X, hence asymmetric). Rounding is applied ONLY at the P02 final-emit stage (`P02_S701_labor_values._round_sig`); `data/intermediate/S701.csv` retains full float64 precision for regression/reproducibility, and downstream S703 consumes the full-precision L01 panels, not the rounded published values.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>- **SIC↔NAICS coarse concordance** (post-1997 sector mapping; DIV-008 reference): productive-classification mapping book ↔ extension is at supersector granularity; finer-grained sector reassignments not yet handled.</t>
-        </is>
-      </c>
+      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>- **1963 benchmark anomaly (WARN-03)**: v1.0 proxy showed S701 = 0.00037 at 1963 (likely IO data gap); v1.1 real implementation may inherit if the gap is in the underlying labeled IO matrix. If V03 surfaces it, document as known_issue rather than re-introducing proxy.</t>
+          <t>## Known issues</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>- **Services sector compensation proxy**: per ST methodology, average compensation `ec_serv` is used as a stand-in for `(ecp)_serv` because BLS production-wage data are unavailable for services. Documented in Appendix G; preserved in v1.1 real implementation.</t>
-        </is>
-      </c>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>- **Agriculture productive-employment proxy**: ST uses mining-sector Lp/L ratio for agriculture (own BLS production-worker data unavailable). Preserved in v1.1.</t>
+          <t>- **BLS CES 2003 overhaul null bridge (DIV-010)**: v1.1 ships factor=1.0 stubs per supersector; non-null factors deferred to v1.2 (BLS Employment Situation news-release archive sourcing). Effect: intra-extension trend from 2003 onward may carry minor methodology-break artifacts; the 1989 SIC↔NAICS anchor reconciliation remains the dominant cross-period level adjustment.</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1811,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>- **Appendix F filter is categorical**: the 85-sector productive/unproductive mask in `Technical/data/source/appendix_F/Table_F_1.csv` is binary (productive=1.0, unproductive=0.0, plus 3 uncertain sectors flagged) rather than fractional. The per-sector fractional shares the user originally envisioned do not literally exist as a published table; within-sector productive ratios are applied at compute time via BLS production-worker series per ST/Mohun methodology.</t>
+          <t>- **SIC↔NAICS coarse concordance** (post-1997 sector mapping; DIV-008 reference): productive-classification mapping book ↔ extension is at supersector granularity; finer-grained sector reassignments not yet handled.</t>
         </is>
       </c>
     </row>
@@ -1827,101 +1819,133 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>- **Six SIC benchmark years only** for book period; no annual interpolation within the book period.</t>
+          <t>- **1963 benchmark anomaly (WARN-03)**: v1.0 proxy showed S701 = 0.00037 at 1963 (likely IO data gap); v1.1 real implementation may inherit if the gap is in the underlying labeled IO matrix. If V03 surfaces it, document as known_issue rather than re-introducing proxy.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>- **Services sector compensation proxy**: per ST methodology, average compensation `ec_serv` is used as a stand-in for `(ecp)_serv` because BLS production-wage data are unavailable for services. Documented in Appendix G; preserved in v1.1 real implementation.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>## Cross-references</t>
+          <t>- **Agriculture productive-employment proxy**: ST uses mining-sector Lp/L ratio for agriculture (own BLS production-worker data unavailable). Preserved in v1.1.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>- **Appendix F filter is categorical**: the 85-sector productive/unproductive mask in `Technical/data/source/appendix_F/Table_F_1.csv` is binary (productive=1.0, unproductive=0.0, plus 3 uncertain sectors flagged) rather than fractional. The per-sector fractional shares the user originally envisioned do not literally exist as a published table; within-sector productive ratios are applied at compute time via BLS production-worker series per ST/Mohun methodology.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>- Upstream: S401 (A-matrix), S402 (Leontief inverse B), Appendix F productive-share filter, Appendix G Table G.2 (sectoral productive employment), BLS CES, BEA NIPA 1.7.5 / GDP-by-Industry</t>
+          <t>- **Six SIC benchmark years only** for book period; no annual interpolation within the book period.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>- Downstream: S702 (prices of production, now also real and sector-disaggregated), S703 (consistent-procedure regression)</t>
-        </is>
-      </c>
+      <c r="B83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>- Related external: Wolff (1977b) symmetric-treatment biases S*/V* upward 4–8%; Khanjian (1989) consistent procedure 6–9% S*/V* deviation; ST 1994 Ch7 §7.4 cross-study critique</t>
+          <t>## Cross-references</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>- Project artifacts: `Technical/Handoffs/CH7_REAL_FIX_PLAN.md`; `Technical/_v1.1_patches/S701_ch7_realfix_patch.json`; `Technical/_v1.1_patches/DIVERGENCE_REGISTER_DIV011_patch.json`</t>
-        </is>
-      </c>
+      <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>- Upstream: S401 (A-matrix), S402 (Leontief inverse B), Appendix F productive-share filter, Appendix G Table G.2 (sectoral productive employment), BLS CES, BEA NIPA 1.7.5 / GDP-by-Industry</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>## Provenance trail</t>
+          <t>- Downstream: S702 (prices of production, now also real and sector-disaggregated), S703 (consistent-procedure regression)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>- Related external: Wolff (1977b) symmetric-treatment biases S*/V* upward 4–8%; Khanjian (1989) consistent procedure 6–9% S*/V* deviation; ST 1994 Ch7 §7.4 cross-study critique</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>- **Original research**: `Technical/research/S701_research.json`, researcher `agent`, 2026-05-06; ported from `predecessor-build/research/T701_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23 (Stage 1 cohort 3 enrichment specifically anchored Ch4 §4.1 equations + Figure 4.3 dimensional check)</t>
+          <t>- Project artifacts: `Technical/Handoffs/CH7_REAL_FIX_PLAN.md`; `Technical/_v1.1_patches/S701_ch7_realfix_patch.json`; `Technical/_v1.1_patches/DIVERGENCE_REGISTER_DIV011_patch.json`</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>- **DPR v1.0**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (proxy disclosure version)</t>
-        </is>
-      </c>
+      <c r="B90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>- **DPR v1.1 (this version)**: 2026-05-24, v1.1 Phase 4 iteration 5 Ch7 real-fix agent 4 (registry/DPR/EPR cohort, parallel to agents 1-3 doing L01/P02 rewrites). Real implementation replaces proxy disclosure. See DIV-011.</t>
+          <t>## Provenance trail</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
-      <c r="B92" t="inlineStr">
+      <c r="B92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>- **Original research**: `Technical/research/S701_research.json`, researcher `agent`, 2026-05-06; ported from `predecessor-build/research/T701_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23 (Stage 1 cohort 3 enrichment specifically anchored Ch4 §4.1 equations + Figure 4.3 dimensional check)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>- **DPR v1.0**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (proxy disclosure version)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>- **DPR v1.1 (this version)**: 2026-05-24, v1.1 Phase 4 iteration 5 Ch7 real-fix agent 4 (registry/DPR/EPR cohort, parallel to agents 1-3 doing L01/P02 rewrites). Real implementation replaces proxy disclosure. See DIV-011.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
         <is>
           <t>- **Anu Framework stage**: Stage 5 EXECUTION (Ch7 real-fix sub-stage); doctor gate IDs P13/P31/P36</t>
         </is>
